--- a/test.xlsx
+++ b/test.xlsx
@@ -11,6 +11,7 @@
     <sheet state="visible" name="gdp_growth" sheetId="6" r:id="rId9"/>
     <sheet state="visible" name="stock_price_index" sheetId="7" r:id="rId10"/>
     <sheet state="visible" name="sovereign_bond_yields" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="capital_flows" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -18,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3662" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3665" uniqueCount="82">
   <si>
     <t>Date</t>
   </si>
@@ -259,6 +260,12 @@
   <si>
     <t>Asia Advanced Economies</t>
   </si>
+  <si>
+    <t>Portfolio Debt</t>
+  </si>
+  <si>
+    <t>Portfolio Equity</t>
+  </si>
 </sst>
 </file>
 
@@ -344,6 +351,10 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -43199,4 +43210,3360 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>36540.0</v>
+      </c>
+      <c r="B2" s="3">
+        <v>-320.7</v>
+      </c>
+      <c r="C2" s="3">
+        <v>3277.0200000000004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>36571.0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>662.9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3496.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>36600.0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1496.8</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5737.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>36631.0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>673.9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>16.68999999999997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>36661.0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>-1693.1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1108.5900000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>36692.0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>-272.1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2985.34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>36722.0</v>
+      </c>
+      <c r="B8" s="3">
+        <v>-70.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>426.8599999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>36753.0</v>
+      </c>
+      <c r="B9" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1699.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>36784.0</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-107.5</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-2236.57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>36814.0</v>
+      </c>
+      <c r="B11" s="3">
+        <v>145.0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>622.1899999999998</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>36845.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-434.8</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1744.0300000000002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>36875.0</v>
+      </c>
+      <c r="B13" s="3">
+        <v>-488.4</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1186.9199999999998</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>36906.0</v>
+      </c>
+      <c r="B14" s="3">
+        <v>-7.1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4664.97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>36937.0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>139.6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>782.85</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>36965.0</v>
+      </c>
+      <c r="B16" s="3">
+        <v>-853.7</v>
+      </c>
+      <c r="C16" s="3">
+        <v>630.07</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>36996.0</v>
+      </c>
+      <c r="B17" s="3">
+        <v>287.6</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1352.59</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>37026.0</v>
+      </c>
+      <c r="B18" s="3">
+        <v>62.1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2467.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>37057.0</v>
+      </c>
+      <c r="B19" s="3">
+        <v>885.5</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1081.6099999999997</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>37087.0</v>
+      </c>
+      <c r="B20" s="3">
+        <v>311.4</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2470.42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>37118.0</v>
+      </c>
+      <c r="B21" s="3">
+        <v>-131.5</v>
+      </c>
+      <c r="C21" s="3">
+        <v>428.12000000000006</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>37149.0</v>
+      </c>
+      <c r="B22" s="3">
+        <v>-1698.6</v>
+      </c>
+      <c r="C22" s="3">
+        <v>-854.8399999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>37179.0</v>
+      </c>
+      <c r="B23" s="3">
+        <v>483.3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2759.6800000000003</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>37210.0</v>
+      </c>
+      <c r="B24" s="3">
+        <v>534.9</v>
+      </c>
+      <c r="C24" s="3">
+        <v>3501.7000000000007</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>37240.0</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1948.1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>722.91</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>37271.0</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1728.9</v>
+      </c>
+      <c r="C26" s="3">
+        <v>984.53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2">
+        <v>37302.0</v>
+      </c>
+      <c r="B27" s="3">
+        <v>-1624.6</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-543.76</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2">
+        <v>37330.0</v>
+      </c>
+      <c r="B28" s="3">
+        <v>-568.2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1063.3600000000004</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2">
+        <v>37361.0</v>
+      </c>
+      <c r="B29" s="3">
+        <v>141.9</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-208.61</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2">
+        <v>37391.0</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1034.9</v>
+      </c>
+      <c r="C30" s="3">
+        <v>-842.68</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>37422.0</v>
+      </c>
+      <c r="B31" s="3">
+        <v>-674.2</v>
+      </c>
+      <c r="C31" s="3">
+        <v>-862.12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2">
+        <v>37452.0</v>
+      </c>
+      <c r="B32" s="3">
+        <v>688.7</v>
+      </c>
+      <c r="C32" s="3">
+        <v>-679.87</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>37483.0</v>
+      </c>
+      <c r="B33" s="3">
+        <v>-450.5</v>
+      </c>
+      <c r="C33" s="3">
+        <v>178.0999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>37514.0</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1299.8</v>
+      </c>
+      <c r="C34" s="3">
+        <v>-1317.7200000000003</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>37544.0</v>
+      </c>
+      <c r="B35" s="3">
+        <v>473.5</v>
+      </c>
+      <c r="C35" s="3">
+        <v>766.47</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>37575.0</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1036.6</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2598.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>37605.0</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1895.9</v>
+      </c>
+      <c r="C37" s="3">
+        <v>386.46000000000004</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>37636.0</v>
+      </c>
+      <c r="B38" s="3">
+        <v>783.6</v>
+      </c>
+      <c r="C38" s="3">
+        <v>963.97</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>37667.0</v>
+      </c>
+      <c r="B39" s="3">
+        <v>-126.9</v>
+      </c>
+      <c r="C39" s="3">
+        <v>-951.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>37695.0</v>
+      </c>
+      <c r="B40" s="3">
+        <v>297.2</v>
+      </c>
+      <c r="C40" s="3">
+        <v>275.96</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>37726.0</v>
+      </c>
+      <c r="B41" s="3">
+        <v>-421.2</v>
+      </c>
+      <c r="C41" s="3">
+        <v>-97.81999999999994</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>37756.0</v>
+      </c>
+      <c r="B42" s="3">
+        <v>462.9</v>
+      </c>
+      <c r="C42" s="3">
+        <v>3163.8600000000006</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>37787.0</v>
+      </c>
+      <c r="B43" s="3">
+        <v>3054.0</v>
+      </c>
+      <c r="C43" s="3">
+        <v>4647.0700000000015</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>37817.0</v>
+      </c>
+      <c r="B44" s="3">
+        <v>54.3</v>
+      </c>
+      <c r="C44" s="3">
+        <v>5018.969999999999</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2">
+        <v>37848.0</v>
+      </c>
+      <c r="B45" s="3">
+        <v>99.9</v>
+      </c>
+      <c r="C45" s="3">
+        <v>4791.17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2">
+        <v>37879.0</v>
+      </c>
+      <c r="B46" s="3">
+        <v>1895.5</v>
+      </c>
+      <c r="C46" s="3">
+        <v>2988.9999999999995</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2">
+        <v>37909.0</v>
+      </c>
+      <c r="B47" s="3">
+        <v>1025.6</v>
+      </c>
+      <c r="C47" s="3">
+        <v>6563.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2">
+        <v>37940.0</v>
+      </c>
+      <c r="B48" s="3">
+        <v>1491.6</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1461.3000000000002</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2">
+        <v>37970.0</v>
+      </c>
+      <c r="B49" s="3">
+        <v>-344.8</v>
+      </c>
+      <c r="C49" s="3">
+        <v>2177.02</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2">
+        <v>38001.0</v>
+      </c>
+      <c r="B50" s="3">
+        <v>82.4</v>
+      </c>
+      <c r="C50" s="3">
+        <v>6931.77</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2">
+        <v>38032.0</v>
+      </c>
+      <c r="B51" s="3">
+        <v>3188.2</v>
+      </c>
+      <c r="C51" s="3">
+        <v>2023.98</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2">
+        <v>38061.0</v>
+      </c>
+      <c r="B52" s="3">
+        <v>1378.5</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1372.0199999999995</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2">
+        <v>38092.0</v>
+      </c>
+      <c r="B53" s="3">
+        <v>-6.2</v>
+      </c>
+      <c r="C53" s="3">
+        <v>2926.14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2">
+        <v>38122.0</v>
+      </c>
+      <c r="B54" s="3">
+        <v>-140.5</v>
+      </c>
+      <c r="C54" s="3">
+        <v>-4863.459999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2">
+        <v>38153.0</v>
+      </c>
+      <c r="B55" s="3">
+        <v>733.8</v>
+      </c>
+      <c r="C55" s="3">
+        <v>504.59999999999997</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2">
+        <v>38183.0</v>
+      </c>
+      <c r="B56" s="3">
+        <v>1115.0</v>
+      </c>
+      <c r="C56" s="3">
+        <v>820.8299999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2">
+        <v>38214.0</v>
+      </c>
+      <c r="B57" s="3">
+        <v>-18.3</v>
+      </c>
+      <c r="C57" s="3">
+        <v>2949.66</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2">
+        <v>38245.0</v>
+      </c>
+      <c r="B58" s="3">
+        <v>-913.1</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1952.07</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2">
+        <v>38275.0</v>
+      </c>
+      <c r="B59" s="3">
+        <v>-212.5</v>
+      </c>
+      <c r="C59" s="3">
+        <v>-79.95999999999981</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2">
+        <v>38306.0</v>
+      </c>
+      <c r="B60" s="3">
+        <v>1782.5</v>
+      </c>
+      <c r="C60" s="3">
+        <v>3087.74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2">
+        <v>38336.0</v>
+      </c>
+      <c r="B61" s="3">
+        <v>1916.2</v>
+      </c>
+      <c r="C61" s="3">
+        <v>-490.21000000000015</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2">
+        <v>38367.0</v>
+      </c>
+      <c r="B62" s="3">
+        <v>-1286.4</v>
+      </c>
+      <c r="C62" s="3">
+        <v>2730.468</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>38398.0</v>
+      </c>
+      <c r="B63" s="3">
+        <v>2157.452362327467</v>
+      </c>
+      <c r="C63" s="3">
+        <v>7593.765999999999</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>38426.0</v>
+      </c>
+      <c r="B64" s="3">
+        <v>1182.567662023521</v>
+      </c>
+      <c r="C64" s="3">
+        <v>-2615.1620000000003</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>38457.0</v>
+      </c>
+      <c r="B65" s="3">
+        <v>-706.4760490568116</v>
+      </c>
+      <c r="C65" s="3">
+        <v>-988.9009999999998</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>38487.0</v>
+      </c>
+      <c r="B66" s="3">
+        <v>1576.2186571703483</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1938.3880000000004</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>38518.0</v>
+      </c>
+      <c r="B67" s="3">
+        <v>1390.4335202761004</v>
+      </c>
+      <c r="C67" s="3">
+        <v>6746.675</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2">
+        <v>38548.0</v>
+      </c>
+      <c r="B68" s="3">
+        <v>1644.3335790753986</v>
+      </c>
+      <c r="C68" s="3">
+        <v>6955.785000000001</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2">
+        <v>38579.0</v>
+      </c>
+      <c r="B69" s="3">
+        <v>919.8609447229967</v>
+      </c>
+      <c r="C69" s="3">
+        <v>656.4390000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>38610.0</v>
+      </c>
+      <c r="B70" s="3">
+        <v>-453.57121046245925</v>
+      </c>
+      <c r="C70" s="3">
+        <v>494.095</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>38640.0</v>
+      </c>
+      <c r="B71" s="3">
+        <v>-1300.796624433376</v>
+      </c>
+      <c r="C71" s="3">
+        <v>-4268.979</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>38671.0</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2342.217941413838</v>
+      </c>
+      <c r="C72" s="3">
+        <v>9117.478000000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>38701.0</v>
+      </c>
+      <c r="B73" s="3">
+        <v>650.9598315698126</v>
+      </c>
+      <c r="C73" s="3">
+        <v>10913.086000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>38732.0</v>
+      </c>
+      <c r="B74" s="3">
+        <v>804.0515235179596</v>
+      </c>
+      <c r="C74" s="3">
+        <v>5820.454</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>38763.0</v>
+      </c>
+      <c r="B75" s="3">
+        <v>2886.375407113824</v>
+      </c>
+      <c r="C75" s="3">
+        <v>7162.300000000001</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>38791.0</v>
+      </c>
+      <c r="B76" s="3">
+        <v>1521.7748909625266</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2414.9259999999995</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>38822.0</v>
+      </c>
+      <c r="B77" s="3">
+        <v>2840.0357898455436</v>
+      </c>
+      <c r="C77" s="3">
+        <v>7070.793</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>38852.0</v>
+      </c>
+      <c r="B78" s="3">
+        <v>1550.2111011621669</v>
+      </c>
+      <c r="C78" s="3">
+        <v>-9603.501</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2">
+        <v>38883.0</v>
+      </c>
+      <c r="B79" s="3">
+        <v>1203.7794505996849</v>
+      </c>
+      <c r="C79" s="3">
+        <v>-2896.8350000000005</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2">
+        <v>38913.0</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2053.60612926449</v>
+      </c>
+      <c r="C80" s="3">
+        <v>-1325.7260000000003</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2">
+        <v>38944.0</v>
+      </c>
+      <c r="B81" s="3">
+        <v>2335.9350062173535</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1258.0839999999998</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2">
+        <v>38975.0</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2348.0124308440427</v>
+      </c>
+      <c r="C82" s="3">
+        <v>2319.0650000000005</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>39005.0</v>
+      </c>
+      <c r="B83" s="3">
+        <v>697.8243008180702</v>
+      </c>
+      <c r="C83" s="3">
+        <v>3631.182</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>39036.0</v>
+      </c>
+      <c r="B84" s="3">
+        <v>3981.281950049079</v>
+      </c>
+      <c r="C84" s="3">
+        <v>3872.9379999999996</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2">
+        <v>39066.0</v>
+      </c>
+      <c r="B85" s="3">
+        <v>1551.175599429667</v>
+      </c>
+      <c r="C85" s="3">
+        <v>1915.1350000000002</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>39097.0</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2418.71370725787</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1041.88</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2">
+        <v>39128.0</v>
+      </c>
+      <c r="B87" s="3">
+        <v>4515.814031298993</v>
+      </c>
+      <c r="C87" s="3">
+        <v>5003.745</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2">
+        <v>39156.0</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1861.3298445776995</v>
+      </c>
+      <c r="C88" s="3">
+        <v>-5111.368000000002</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2">
+        <v>39187.0</v>
+      </c>
+      <c r="B89" s="3">
+        <v>8997.412072778197</v>
+      </c>
+      <c r="C89" s="3">
+        <v>7402.415999999999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2">
+        <v>39217.0</v>
+      </c>
+      <c r="B90" s="3">
+        <v>11082.225364447144</v>
+      </c>
+      <c r="C90" s="3">
+        <v>3617.92</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>39248.0</v>
+      </c>
+      <c r="B91" s="3">
+        <v>999.534189044163</v>
+      </c>
+      <c r="C91" s="3">
+        <v>5219.253</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>39278.0</v>
+      </c>
+      <c r="B92" s="3">
+        <v>3925.308600642833</v>
+      </c>
+      <c r="C92" s="3">
+        <v>876.8059999999991</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>39309.0</v>
+      </c>
+      <c r="B93" s="3">
+        <v>4135.214314301701</v>
+      </c>
+      <c r="C93" s="3">
+        <v>-18226.17</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2">
+        <v>39340.0</v>
+      </c>
+      <c r="B94" s="3">
+        <v>7050.798524798551</v>
+      </c>
+      <c r="C94" s="3">
+        <v>6465.569000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>39370.0</v>
+      </c>
+      <c r="B95" s="3">
+        <v>9494.85565823712</v>
+      </c>
+      <c r="C95" s="3">
+        <v>7792.483000000003</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>39401.0</v>
+      </c>
+      <c r="B96" s="3">
+        <v>11669.452532159408</v>
+      </c>
+      <c r="C96" s="3">
+        <v>-15328.626</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2">
+        <v>39431.0</v>
+      </c>
+      <c r="B97" s="3">
+        <v>10099.965880368218</v>
+      </c>
+      <c r="C97" s="3">
+        <v>-1207.305</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2">
+        <v>39462.0</v>
+      </c>
+      <c r="B98" s="3">
+        <v>11078.047214829376</v>
+      </c>
+      <c r="C98" s="3">
+        <v>-15876.056999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2">
+        <v>39493.0</v>
+      </c>
+      <c r="B99" s="3">
+        <v>7754.558216712232</v>
+      </c>
+      <c r="C99" s="3">
+        <v>2980.1609999999996</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2">
+        <v>39522.0</v>
+      </c>
+      <c r="B100" s="3">
+        <v>2431.135109577603</v>
+      </c>
+      <c r="C100" s="3">
+        <v>-4098.311000000001</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2">
+        <v>39553.0</v>
+      </c>
+      <c r="B101" s="3">
+        <v>9735.743082134526</v>
+      </c>
+      <c r="C101" s="3">
+        <v>-768.3590000000002</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2">
+        <v>39583.0</v>
+      </c>
+      <c r="B102" s="3">
+        <v>3165.1820795785616</v>
+      </c>
+      <c r="C102" s="3">
+        <v>354.04499999999973</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2">
+        <v>39614.0</v>
+      </c>
+      <c r="B103" s="3">
+        <v>-1581.8976725478485</v>
+      </c>
+      <c r="C103" s="3">
+        <v>-12793.078</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2">
+        <v>39644.0</v>
+      </c>
+      <c r="B104" s="3">
+        <v>-3526.9578348611603</v>
+      </c>
+      <c r="C104" s="3">
+        <v>-9352.043999999998</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2">
+        <v>39675.0</v>
+      </c>
+      <c r="B105" s="3">
+        <v>-3306.50833630932</v>
+      </c>
+      <c r="C105" s="3">
+        <v>-4490.316</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2">
+        <v>39706.0</v>
+      </c>
+      <c r="B106" s="3">
+        <v>-7206.5113268175155</v>
+      </c>
+      <c r="C106" s="3">
+        <v>-8325.412</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2">
+        <v>39736.0</v>
+      </c>
+      <c r="B107" s="3">
+        <v>-9518.093096069524</v>
+      </c>
+      <c r="C107" s="3">
+        <v>-10574.008999999998</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2">
+        <v>39767.0</v>
+      </c>
+      <c r="B108" s="3">
+        <v>-5817.534984238542</v>
+      </c>
+      <c r="C108" s="3">
+        <v>-3670.7079999999996</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2">
+        <v>39797.0</v>
+      </c>
+      <c r="B109" s="3">
+        <v>-1132.488538691756</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1747.4389999999999</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2">
+        <v>39828.0</v>
+      </c>
+      <c r="B110" s="3">
+        <v>3012.400304200927</v>
+      </c>
+      <c r="C110" s="3">
+        <v>-2579.3759999999997</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2">
+        <v>39859.0</v>
+      </c>
+      <c r="B111" s="3">
+        <v>-1196.613459669582</v>
+      </c>
+      <c r="C111" s="3">
+        <v>-1850.665</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2">
+        <v>39887.0</v>
+      </c>
+      <c r="B112" s="3">
+        <v>-4816.105177882052</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1997.8890000000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2">
+        <v>39918.0</v>
+      </c>
+      <c r="B113" s="3">
+        <v>6883.01648576061</v>
+      </c>
+      <c r="C113" s="3">
+        <v>7278.976</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2">
+        <v>39948.0</v>
+      </c>
+      <c r="B114" s="3">
+        <v>2583.828078791826</v>
+      </c>
+      <c r="C114" s="3">
+        <v>10010.221</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2">
+        <v>39979.0</v>
+      </c>
+      <c r="B115" s="3">
+        <v>2922.5698329681045</v>
+      </c>
+      <c r="C115" s="3">
+        <v>4071.0230000000006</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2">
+        <v>40009.0</v>
+      </c>
+      <c r="B116" s="3">
+        <v>8091.664147113116</v>
+      </c>
+      <c r="C116" s="3">
+        <v>9365.648</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2">
+        <v>40040.0</v>
+      </c>
+      <c r="B117" s="3">
+        <v>1434.930368844884</v>
+      </c>
+      <c r="C117" s="3">
+        <v>5154.268</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2">
+        <v>40071.0</v>
+      </c>
+      <c r="B118" s="3">
+        <v>6001.936768670609</v>
+      </c>
+      <c r="C118" s="3">
+        <v>14077.776000000002</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2">
+        <v>40101.0</v>
+      </c>
+      <c r="B119" s="3">
+        <v>9875.305036371003</v>
+      </c>
+      <c r="C119" s="3">
+        <v>2916.5919999999996</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2">
+        <v>40132.0</v>
+      </c>
+      <c r="B120" s="3">
+        <v>1245.863061168774</v>
+      </c>
+      <c r="C120" s="3">
+        <v>2790.3199999999997</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2">
+        <v>40162.0</v>
+      </c>
+      <c r="B121" s="3">
+        <v>-411.5085485763924</v>
+      </c>
+      <c r="C121" s="3">
+        <v>7337.628</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2">
+        <v>40193.0</v>
+      </c>
+      <c r="B122" s="3">
+        <v>2227.7228653680213</v>
+      </c>
+      <c r="C122" s="3">
+        <v>677.0749999999997</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2">
+        <v>40224.0</v>
+      </c>
+      <c r="B123" s="3">
+        <v>2374.6583359274696</v>
+      </c>
+      <c r="C123" s="3">
+        <v>-2172.161</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2">
+        <v>40252.0</v>
+      </c>
+      <c r="B124" s="3">
+        <v>12273.052110923023</v>
+      </c>
+      <c r="C124" s="3">
+        <v>14634.064999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2">
+        <v>40283.0</v>
+      </c>
+      <c r="B125" s="3">
+        <v>8565.897777891729</v>
+      </c>
+      <c r="C125" s="3">
+        <v>11232.58</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
+        <v>40313.0</v>
+      </c>
+      <c r="B126" s="3">
+        <v>3112.0369100843222</v>
+      </c>
+      <c r="C126" s="3">
+        <v>-11807.876999999997</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2">
+        <v>40344.0</v>
+      </c>
+      <c r="B127" s="3">
+        <v>3045.5812798861034</v>
+      </c>
+      <c r="C127" s="3">
+        <v>4007.29</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2">
+        <v>40374.0</v>
+      </c>
+      <c r="B128" s="3">
+        <v>11892.833822256871</v>
+      </c>
+      <c r="C128" s="3">
+        <v>9247.711000000001</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2">
+        <v>40405.0</v>
+      </c>
+      <c r="B129" s="3">
+        <v>4860.224171920538</v>
+      </c>
+      <c r="C129" s="3">
+        <v>2444.466999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2">
+        <v>40436.0</v>
+      </c>
+      <c r="B130" s="3">
+        <v>9035.133069639312</v>
+      </c>
+      <c r="C130" s="3">
+        <v>15740.771999999999</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2">
+        <v>40466.0</v>
+      </c>
+      <c r="B131" s="3">
+        <v>11348.73282632205</v>
+      </c>
+      <c r="C131" s="3">
+        <v>13477.211000000001</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2">
+        <v>40497.0</v>
+      </c>
+      <c r="B132" s="3">
+        <v>741.9029627941085</v>
+      </c>
+      <c r="C132" s="3">
+        <v>7214.175000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2">
+        <v>40527.0</v>
+      </c>
+      <c r="B133" s="3">
+        <v>-2907.976697842359</v>
+      </c>
+      <c r="C133" s="3">
+        <v>9193.032000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2">
+        <v>40558.0</v>
+      </c>
+      <c r="B134" s="3">
+        <v>10932.766537207242</v>
+      </c>
+      <c r="C134" s="3">
+        <v>2166.5140000000006</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2">
+        <v>40589.0</v>
+      </c>
+      <c r="B135" s="3">
+        <v>7247.26954846745</v>
+      </c>
+      <c r="C135" s="3">
+        <v>-8084.721999999999</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2">
+        <v>40617.0</v>
+      </c>
+      <c r="B136" s="3">
+        <v>9896.955017740629</v>
+      </c>
+      <c r="C136" s="3">
+        <v>-195.42499999999978</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2">
+        <v>40648.0</v>
+      </c>
+      <c r="B137" s="3">
+        <v>18035.52511644927</v>
+      </c>
+      <c r="C137" s="3">
+        <v>12841.913999999999</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2">
+        <v>40678.0</v>
+      </c>
+      <c r="B138" s="3">
+        <v>6967.037699662638</v>
+      </c>
+      <c r="C138" s="3">
+        <v>-3702.0540000000005</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2">
+        <v>40709.0</v>
+      </c>
+      <c r="B139" s="3">
+        <v>4353.579317125953</v>
+      </c>
+      <c r="C139" s="3">
+        <v>-263.8050000000005</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2">
+        <v>40739.0</v>
+      </c>
+      <c r="B140" s="3">
+        <v>13757.435319634962</v>
+      </c>
+      <c r="C140" s="3">
+        <v>4070.5170000000003</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2">
+        <v>40770.0</v>
+      </c>
+      <c r="B141" s="3">
+        <v>3245.4198251047487</v>
+      </c>
+      <c r="C141" s="3">
+        <v>-18201.064000000002</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2">
+        <v>40801.0</v>
+      </c>
+      <c r="B142" s="3">
+        <v>-7455.537377962199</v>
+      </c>
+      <c r="C142" s="3">
+        <v>-4263.669999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2">
+        <v>40831.0</v>
+      </c>
+      <c r="B143" s="3">
+        <v>4677.693508394712</v>
+      </c>
+      <c r="C143" s="3">
+        <v>5116.471</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2">
+        <v>40862.0</v>
+      </c>
+      <c r="B144" s="3">
+        <v>2124.939528862875</v>
+      </c>
+      <c r="C144" s="3">
+        <v>-5292.952</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2">
+        <v>40892.0</v>
+      </c>
+      <c r="B145" s="3">
+        <v>1271.0277013992818</v>
+      </c>
+      <c r="C145" s="3">
+        <v>2832.9429999999998</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2">
+        <v>40923.0</v>
+      </c>
+      <c r="B146" s="3">
+        <v>16368.220310683313</v>
+      </c>
+      <c r="C146" s="3">
+        <v>10662.002</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2">
+        <v>40954.0</v>
+      </c>
+      <c r="B147" s="3">
+        <v>12467.234868485752</v>
+      </c>
+      <c r="C147" s="3">
+        <v>12386.242</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2">
+        <v>40983.0</v>
+      </c>
+      <c r="B148" s="3">
+        <v>6092.783164766388</v>
+      </c>
+      <c r="C148" s="3">
+        <v>6402.752000000002</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2">
+        <v>41014.0</v>
+      </c>
+      <c r="B149" s="3">
+        <v>-694.7036778623072</v>
+      </c>
+      <c r="C149" s="3">
+        <v>-893.6369999999998</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2">
+        <v>41044.0</v>
+      </c>
+      <c r="B150" s="3">
+        <v>3343.081279474456</v>
+      </c>
+      <c r="C150" s="3">
+        <v>-8568.104</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2">
+        <v>41075.0</v>
+      </c>
+      <c r="B151" s="3">
+        <v>3991.1198684808805</v>
+      </c>
+      <c r="C151" s="3">
+        <v>-1462.9699999999998</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2">
+        <v>41105.0</v>
+      </c>
+      <c r="B152" s="3">
+        <v>11067.127913920602</v>
+      </c>
+      <c r="C152" s="3">
+        <v>1737.1629999999998</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2">
+        <v>41136.0</v>
+      </c>
+      <c r="B153" s="3">
+        <v>-216.4945629569381</v>
+      </c>
+      <c r="C153" s="3">
+        <v>11213.647</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2">
+        <v>41167.0</v>
+      </c>
+      <c r="B154" s="3">
+        <v>12172.817599738186</v>
+      </c>
+      <c r="C154" s="3">
+        <v>11100.334000000003</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2">
+        <v>41197.0</v>
+      </c>
+      <c r="B155" s="3">
+        <v>6522.016275973027</v>
+      </c>
+      <c r="C155" s="3">
+        <v>-186.3579999999997</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2">
+        <v>41228.0</v>
+      </c>
+      <c r="B156" s="3">
+        <v>5180.842446358305</v>
+      </c>
+      <c r="C156" s="3">
+        <v>2681.6449999999995</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2">
+        <v>41258.0</v>
+      </c>
+      <c r="B157" s="3">
+        <v>5759.811359195528</v>
+      </c>
+      <c r="C157" s="3">
+        <v>11503.441</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2">
+        <v>41289.0</v>
+      </c>
+      <c r="B158" s="3">
+        <v>4932.697284342943</v>
+      </c>
+      <c r="C158" s="3">
+        <v>5057.517000000001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2">
+        <v>41320.0</v>
+      </c>
+      <c r="B159" s="3">
+        <v>5047.982687252201</v>
+      </c>
+      <c r="C159" s="3">
+        <v>7667.654</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2">
+        <v>41348.0</v>
+      </c>
+      <c r="B160" s="3">
+        <v>8545.43178519725</v>
+      </c>
+      <c r="C160" s="3">
+        <v>881.9299999999994</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2">
+        <v>41379.0</v>
+      </c>
+      <c r="B161" s="3">
+        <v>12929.387551348107</v>
+      </c>
+      <c r="C161" s="3">
+        <v>392.3289999999996</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2">
+        <v>41409.0</v>
+      </c>
+      <c r="B162" s="3">
+        <v>1129.2267421781878</v>
+      </c>
+      <c r="C162" s="3">
+        <v>7227.919</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2">
+        <v>41440.0</v>
+      </c>
+      <c r="B163" s="3">
+        <v>-11170.401838736725</v>
+      </c>
+      <c r="C163" s="3">
+        <v>-16175.69</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2">
+        <v>41470.0</v>
+      </c>
+      <c r="B164" s="3">
+        <v>-1634.2617601834959</v>
+      </c>
+      <c r="C164" s="3">
+        <v>2738.3200000000006</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2">
+        <v>41501.0</v>
+      </c>
+      <c r="B165" s="3">
+        <v>-3463.09612879588</v>
+      </c>
+      <c r="C165" s="3">
+        <v>-5346.425</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2">
+        <v>41532.0</v>
+      </c>
+      <c r="B166" s="3">
+        <v>7523.915686891502</v>
+      </c>
+      <c r="C166" s="3">
+        <v>15712.862000000001</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2">
+        <v>41562.0</v>
+      </c>
+      <c r="B167" s="3">
+        <v>5217.7143207251365</v>
+      </c>
+      <c r="C167" s="3">
+        <v>11139.873000000001</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2">
+        <v>41593.0</v>
+      </c>
+      <c r="B168" s="3">
+        <v>-3507.169920079325</v>
+      </c>
+      <c r="C168" s="3">
+        <v>-2694.8600000000006</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2">
+        <v>41623.0</v>
+      </c>
+      <c r="B169" s="3">
+        <v>1761.2388852404335</v>
+      </c>
+      <c r="C169" s="3">
+        <v>-58.85999999999886</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2">
+        <v>41654.0</v>
+      </c>
+      <c r="B170" s="3">
+        <v>2349.168627639162</v>
+      </c>
+      <c r="C170" s="3">
+        <v>-1292.875</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2">
+        <v>41685.0</v>
+      </c>
+      <c r="B171" s="3">
+        <v>1474.7411913618937</v>
+      </c>
+      <c r="C171" s="3">
+        <v>-1580.2990000000004</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2">
+        <v>41713.0</v>
+      </c>
+      <c r="B172" s="3">
+        <v>4435.652635714773</v>
+      </c>
+      <c r="C172" s="3">
+        <v>6505.245</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2">
+        <v>41744.0</v>
+      </c>
+      <c r="B173" s="3">
+        <v>2837.749990162091</v>
+      </c>
+      <c r="C173" s="3">
+        <v>10455.527</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2">
+        <v>41774.0</v>
+      </c>
+      <c r="B174" s="3">
+        <v>7261.490817115043</v>
+      </c>
+      <c r="C174" s="3">
+        <v>6740.763</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2">
+        <v>41805.0</v>
+      </c>
+      <c r="B175" s="3">
+        <v>4315.618098159279</v>
+      </c>
+      <c r="C175" s="3">
+        <v>6134.699000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2">
+        <v>41835.0</v>
+      </c>
+      <c r="B176" s="3">
+        <v>11899.767423673695</v>
+      </c>
+      <c r="C176" s="3">
+        <v>8487.67</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2">
+        <v>41866.0</v>
+      </c>
+      <c r="B177" s="3">
+        <v>3955.8981639748717</v>
+      </c>
+      <c r="C177" s="3">
+        <v>5642.236999999999</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2">
+        <v>41897.0</v>
+      </c>
+      <c r="B178" s="3">
+        <v>330.370506238862</v>
+      </c>
+      <c r="C178" s="3">
+        <v>-1849.313</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2">
+        <v>41927.0</v>
+      </c>
+      <c r="B179" s="3">
+        <v>7091.033949318885</v>
+      </c>
+      <c r="C179" s="3">
+        <v>-3472.106</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2">
+        <v>41958.0</v>
+      </c>
+      <c r="B180" s="3">
+        <v>1101.0546884820408</v>
+      </c>
+      <c r="C180" s="3">
+        <v>8749.211999999998</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2">
+        <v>41988.0</v>
+      </c>
+      <c r="B181" s="3">
+        <v>-2716.281086735746</v>
+      </c>
+      <c r="C181" s="3">
+        <v>-6247.214000000001</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2">
+        <v>42019.0</v>
+      </c>
+      <c r="B182" s="3">
+        <v>7413.214827055814</v>
+      </c>
+      <c r="C182" s="3">
+        <v>6004.707167003773</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2">
+        <v>42050.0</v>
+      </c>
+      <c r="B183" s="3">
+        <v>186.6702641970295</v>
+      </c>
+      <c r="C183" s="3">
+        <v>8795.372230629353</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2">
+        <v>42078.0</v>
+      </c>
+      <c r="B184" s="3">
+        <v>10423.150670925797</v>
+      </c>
+      <c r="C184" s="3">
+        <v>4847.474702366872</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2">
+        <v>42109.0</v>
+      </c>
+      <c r="B185" s="3">
+        <v>-4094.797951568473</v>
+      </c>
+      <c r="C185" s="3">
+        <v>13002.52441711078</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2">
+        <v>42139.0</v>
+      </c>
+      <c r="B186" s="3">
+        <v>4824.363904219279</v>
+      </c>
+      <c r="C186" s="3">
+        <v>8330.59377040704</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2">
+        <v>42170.0</v>
+      </c>
+      <c r="B187" s="3">
+        <v>3374.2019784100494</v>
+      </c>
+      <c r="C187" s="3">
+        <v>-541.9887875178364</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2">
+        <v>42200.0</v>
+      </c>
+      <c r="B188" s="3">
+        <v>-1910.4177309696483</v>
+      </c>
+      <c r="C188" s="3">
+        <v>-11195.64792811876</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2">
+        <v>42231.0</v>
+      </c>
+      <c r="B189" s="3">
+        <v>-12408.90360897584</v>
+      </c>
+      <c r="C189" s="3">
+        <v>-9612.54982666482</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2">
+        <v>42262.0</v>
+      </c>
+      <c r="B190" s="3">
+        <v>-5997.215013860107</v>
+      </c>
+      <c r="C190" s="3">
+        <v>-5218.249945216414</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2">
+        <v>42292.0</v>
+      </c>
+      <c r="B191" s="3">
+        <v>-1644.8245225903463</v>
+      </c>
+      <c r="C191" s="3">
+        <v>3809.2791095504963</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2">
+        <v>42323.0</v>
+      </c>
+      <c r="B192" s="3">
+        <v>4167.453168685539</v>
+      </c>
+      <c r="C192" s="3">
+        <v>-5566.106842378131</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2">
+        <v>42353.0</v>
+      </c>
+      <c r="B193" s="3">
+        <v>-8395.184960397466</v>
+      </c>
+      <c r="C193" s="3">
+        <v>-4520.358367172345</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2">
+        <v>42384.0</v>
+      </c>
+      <c r="B194" s="3">
+        <v>-15379.561500918899</v>
+      </c>
+      <c r="C194" s="3">
+        <v>-5447.477872330131</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2">
+        <v>42415.0</v>
+      </c>
+      <c r="B195" s="3">
+        <v>-7280.248012621035</v>
+      </c>
+      <c r="C195" s="3">
+        <v>1242.5023554643117</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2">
+        <v>42444.0</v>
+      </c>
+      <c r="B196" s="3">
+        <v>3403.0712056966486</v>
+      </c>
+      <c r="C196" s="3">
+        <v>17891.161516865817</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2">
+        <v>42475.0</v>
+      </c>
+      <c r="B197" s="3">
+        <v>13025.086026920875</v>
+      </c>
+      <c r="C197" s="3">
+        <v>3647.7585803790003</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2">
+        <v>42505.0</v>
+      </c>
+      <c r="B198" s="3">
+        <v>8404.09548594649</v>
+      </c>
+      <c r="C198" s="3">
+        <v>-1327.3384587427292</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2">
+        <v>42536.0</v>
+      </c>
+      <c r="B199" s="3">
+        <v>7601.129021642049</v>
+      </c>
+      <c r="C199" s="3">
+        <v>5907.764478363731</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2">
+        <v>42566.0</v>
+      </c>
+      <c r="B200" s="3">
+        <v>5043.46352358751</v>
+      </c>
+      <c r="C200" s="3">
+        <v>18696.78232933719</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2">
+        <v>42597.0</v>
+      </c>
+      <c r="B201" s="3">
+        <v>10524.181287951953</v>
+      </c>
+      <c r="C201" s="3">
+        <v>13860.192247409484</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2">
+        <v>42628.0</v>
+      </c>
+      <c r="B202" s="3">
+        <v>3835.7848545664688</v>
+      </c>
+      <c r="C202" s="3">
+        <v>6330.037623253324</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2">
+        <v>42658.0</v>
+      </c>
+      <c r="B203" s="3">
+        <v>-3177.9364591386875</v>
+      </c>
+      <c r="C203" s="3">
+        <v>93.58788235872551</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2">
+        <v>42689.0</v>
+      </c>
+      <c r="B204" s="3">
+        <v>-4508.97133426453</v>
+      </c>
+      <c r="C204" s="3">
+        <v>-7805.855310147556</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2">
+        <v>42719.0</v>
+      </c>
+      <c r="B205" s="3">
+        <v>293.81533454177986</v>
+      </c>
+      <c r="C205" s="3">
+        <v>119.6796277888308</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2">
+        <v>42750.0</v>
+      </c>
+      <c r="B206" s="3">
+        <v>7001.299323712152</v>
+      </c>
+      <c r="C206" s="3">
+        <v>5117.737035594597</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2">
+        <v>42781.0</v>
+      </c>
+      <c r="B207" s="3">
+        <v>3482.599033312245</v>
+      </c>
+      <c r="C207" s="3">
+        <v>8470.007745815477</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2">
+        <v>42809.0</v>
+      </c>
+      <c r="B208" s="3">
+        <v>4839.500712028055</v>
+      </c>
+      <c r="C208" s="3">
+        <v>14670.345718589922</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2">
+        <v>42840.0</v>
+      </c>
+      <c r="B209" s="3">
+        <v>13160.745209260514</v>
+      </c>
+      <c r="C209" s="3">
+        <v>4898.9553520760965</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2">
+        <v>42870.0</v>
+      </c>
+      <c r="B210" s="3">
+        <v>10161.34147700595</v>
+      </c>
+      <c r="C210" s="3">
+        <v>9564.318915888342</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2">
+        <v>42901.0</v>
+      </c>
+      <c r="B211" s="3">
+        <v>6807.068887823242</v>
+      </c>
+      <c r="C211" s="3">
+        <v>5640.628232035563</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2">
+        <v>42931.0</v>
+      </c>
+      <c r="B212" s="3">
+        <v>18233.623743840886</v>
+      </c>
+      <c r="C212" s="3">
+        <v>4370.664739899954</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2">
+        <v>42962.0</v>
+      </c>
+      <c r="B213" s="3">
+        <v>17243.59120147605</v>
+      </c>
+      <c r="C213" s="3">
+        <v>202.08565969394817</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2">
+        <v>42993.0</v>
+      </c>
+      <c r="B214" s="3">
+        <v>21477.6972277101</v>
+      </c>
+      <c r="C214" s="3">
+        <v>-1729.4155995939013</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2">
+        <v>43023.0</v>
+      </c>
+      <c r="B215" s="3">
+        <v>19305.723141940653</v>
+      </c>
+      <c r="C215" s="3">
+        <v>6363.363513785073</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2">
+        <v>43054.0</v>
+      </c>
+      <c r="B216" s="3">
+        <v>11854.365310571833</v>
+      </c>
+      <c r="C216" s="3">
+        <v>4068.9704603639425</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2">
+        <v>43084.0</v>
+      </c>
+      <c r="B217" s="3">
+        <v>6466.443868012665</v>
+      </c>
+      <c r="C217" s="3">
+        <v>-2515.0228741490155</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2">
+        <v>43115.0</v>
+      </c>
+      <c r="B218" s="3">
+        <v>31373.329217347255</v>
+      </c>
+      <c r="C218" s="3">
+        <v>18245.78460997431</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2">
+        <v>43146.0</v>
+      </c>
+      <c r="B219" s="3">
+        <v>4169.008319180087</v>
+      </c>
+      <c r="C219" s="3">
+        <v>-10272.881834186112</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2">
+        <v>43174.0</v>
+      </c>
+      <c r="B220" s="3">
+        <v>11532.710884226857</v>
+      </c>
+      <c r="C220" s="3">
+        <v>2543.019824211805</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2">
+        <v>43205.0</v>
+      </c>
+      <c r="B221" s="3">
+        <v>9911.891156287596</v>
+      </c>
+      <c r="C221" s="3">
+        <v>204.6778085892276</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2">
+        <v>43235.0</v>
+      </c>
+      <c r="B222" s="3">
+        <v>12989.706013614397</v>
+      </c>
+      <c r="C222" s="3">
+        <v>3949.2334129600385</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2">
+        <v>43266.0</v>
+      </c>
+      <c r="B223" s="3">
+        <v>16654.686618855663</v>
+      </c>
+      <c r="C223" s="3">
+        <v>-2165.902221549265</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2">
+        <v>43296.0</v>
+      </c>
+      <c r="B224" s="3">
+        <v>16288.62745720992</v>
+      </c>
+      <c r="C224" s="3">
+        <v>4478.0055712677995</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2">
+        <v>43327.0</v>
+      </c>
+      <c r="B225" s="3">
+        <v>25186.277986197318</v>
+      </c>
+      <c r="C225" s="3">
+        <v>7271.397818787554</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2">
+        <v>43358.0</v>
+      </c>
+      <c r="B226" s="3">
+        <v>459.3583868865798</v>
+      </c>
+      <c r="C226" s="3">
+        <v>4080.4482099446464</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2">
+        <v>43388.0</v>
+      </c>
+      <c r="B227" s="3">
+        <v>2159.50766137582</v>
+      </c>
+      <c r="C227" s="3">
+        <v>-15205.624766904086</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2">
+        <v>43419.0</v>
+      </c>
+      <c r="B228" s="3">
+        <v>-4197.912441992333</v>
+      </c>
+      <c r="C228" s="3">
+        <v>10327.374651781909</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2">
+        <v>43449.0</v>
+      </c>
+      <c r="B229" s="3">
+        <v>5671.34113346204</v>
+      </c>
+      <c r="C229" s="3">
+        <v>1438.555815122174</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2">
+        <v>43480.0</v>
+      </c>
+      <c r="B230" s="3">
+        <v>416.38395986939776</v>
+      </c>
+      <c r="C230" s="3">
+        <v>17538.119729541995</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2">
+        <v>43511.0</v>
+      </c>
+      <c r="B231" s="3">
+        <v>12843.592251124688</v>
+      </c>
+      <c r="C231" s="3">
+        <v>14773.183411875521</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2">
+        <v>43539.0</v>
+      </c>
+      <c r="B232" s="3">
+        <v>9252.529138935255</v>
+      </c>
+      <c r="C232" s="3">
+        <v>7122.724858582483</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2">
+        <v>43570.0</v>
+      </c>
+      <c r="B233" s="3">
+        <v>6751.400776907172</v>
+      </c>
+      <c r="C233" s="3">
+        <v>3834.558439079061</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2">
+        <v>43600.0</v>
+      </c>
+      <c r="B234" s="3">
+        <v>12594.623847310539</v>
+      </c>
+      <c r="C234" s="3">
+        <v>-16543.837385086685</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2">
+        <v>43631.0</v>
+      </c>
+      <c r="B235" s="3">
+        <v>23286.110154320286</v>
+      </c>
+      <c r="C235" s="3">
+        <v>7303.222546007626</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2">
+        <v>43661.0</v>
+      </c>
+      <c r="B236" s="3">
+        <v>14686.45831269175</v>
+      </c>
+      <c r="C236" s="3">
+        <v>1147.6530357592687</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2">
+        <v>43692.0</v>
+      </c>
+      <c r="B237" s="3">
+        <v>2365.589044731649</v>
+      </c>
+      <c r="C237" s="3">
+        <v>-9152.311246296766</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2">
+        <v>43723.0</v>
+      </c>
+      <c r="B238" s="3">
+        <v>17730.802371107748</v>
+      </c>
+      <c r="C238" s="3">
+        <v>10278.108710537499</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2">
+        <v>43753.0</v>
+      </c>
+      <c r="B239" s="3">
+        <v>20430.292631227738</v>
+      </c>
+      <c r="C239" s="3">
+        <v>10616.86449362786</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2">
+        <v>43784.0</v>
+      </c>
+      <c r="B240" s="3">
+        <v>3320.4794078431205</v>
+      </c>
+      <c r="C240" s="3">
+        <v>10122.50193209138</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2">
+        <v>43814.0</v>
+      </c>
+      <c r="B241" s="3">
+        <v>-6627.050016648075</v>
+      </c>
+      <c r="C241" s="3">
+        <v>13577.427574280766</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2">
+        <v>43845.0</v>
+      </c>
+      <c r="B242" s="3">
+        <v>11422.395516329898</v>
+      </c>
+      <c r="C242" s="3">
+        <v>2833.550305361118</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2">
+        <v>43876.0</v>
+      </c>
+      <c r="B243" s="3">
+        <v>864.7851444059673</v>
+      </c>
+      <c r="C243" s="3">
+        <v>-9938.640852546388</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2">
+        <v>43905.0</v>
+      </c>
+      <c r="B244" s="3">
+        <v>-19139.01218334642</v>
+      </c>
+      <c r="C244" s="3">
+        <v>-48448.71845281473</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2">
+        <v>43936.0</v>
+      </c>
+      <c r="B245" s="3">
+        <v>-8142.762944457598</v>
+      </c>
+      <c r="C245" s="3">
+        <v>3894.0221559177035</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2">
+        <v>43966.0</v>
+      </c>
+      <c r="B246" s="3">
+        <v>31003.966591965112</v>
+      </c>
+      <c r="C246" s="3">
+        <v>-1580.4200144760264</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2">
+        <v>43997.0</v>
+      </c>
+      <c r="B247" s="3">
+        <v>31182.946966654363</v>
+      </c>
+      <c r="C247" s="3">
+        <v>13808.099858558324</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2">
+        <v>44027.0</v>
+      </c>
+      <c r="B248" s="3">
+        <v>40306.0509646253</v>
+      </c>
+      <c r="C248" s="3">
+        <v>1755.8220898735024</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2">
+        <v>44058.0</v>
+      </c>
+      <c r="B249" s="3">
+        <v>20414.855092796613</v>
+      </c>
+      <c r="C249" s="3">
+        <v>748.3816922287849</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2">
+        <v>44089.0</v>
+      </c>
+      <c r="B250" s="3">
+        <v>31989.33602904286</v>
+      </c>
+      <c r="C250" s="3">
+        <v>-10426.67008210229</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2">
+        <v>44119.0</v>
+      </c>
+      <c r="B251" s="3">
+        <v>29219.135729650534</v>
+      </c>
+      <c r="C251" s="3">
+        <v>8385.551725786723</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2">
+        <v>44150.0</v>
+      </c>
+      <c r="B252" s="3">
+        <v>36103.88767832232</v>
+      </c>
+      <c r="C252" s="3">
+        <v>32741.6858800132</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2">
+        <v>44180.0</v>
+      </c>
+      <c r="B253" s="3">
+        <v>14471.816811585966</v>
+      </c>
+      <c r="C253" s="3">
+        <v>27694.538194200086</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2">
+        <v>44211.0</v>
+      </c>
+      <c r="B254" s="3">
+        <v>47305.393493962954</v>
+      </c>
+      <c r="C254" s="3">
+        <v>-1601.51716489157</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2">
+        <v>44242.0</v>
+      </c>
+      <c r="B255" s="3">
+        <v>43038.04509844511</v>
+      </c>
+      <c r="C255" s="3">
+        <v>1849.8835366608234</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2">
+        <v>44270.0</v>
+      </c>
+      <c r="B256" s="3">
+        <v>-5374.097844403788</v>
+      </c>
+      <c r="C256" s="3">
+        <v>-4574.679671769254</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2">
+        <v>44301.0</v>
+      </c>
+      <c r="B257" s="3">
+        <v>14031.357458388398</v>
+      </c>
+      <c r="C257" s="3">
+        <v>11750.515042660638</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2">
+        <v>44331.0</v>
+      </c>
+      <c r="B258" s="3">
+        <v>3536.6103235853316</v>
+      </c>
+      <c r="C258" s="3">
+        <v>1287.4342224540776</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2">
+        <v>44362.0</v>
+      </c>
+      <c r="B259" s="3">
+        <v>24824.930672505172</v>
+      </c>
+      <c r="C259" s="3">
+        <v>3841.259634885286</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2">
+        <v>44392.0</v>
+      </c>
+      <c r="B260" s="3">
+        <v>15053.535596490829</v>
+      </c>
+      <c r="C260" s="3">
+        <v>-5672.260638012698</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2">
+        <v>44423.0</v>
+      </c>
+      <c r="B261" s="3">
+        <v>7778.705730499219</v>
+      </c>
+      <c r="C261" s="3">
+        <v>5321.346774524096</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2">
+        <v>44454.0</v>
+      </c>
+      <c r="B262" s="3">
+        <v>8955.327403466446</v>
+      </c>
+      <c r="C262" s="3">
+        <v>5153.532785710824</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2">
+        <v>44484.0</v>
+      </c>
+      <c r="B263" s="3">
+        <v>20396.12534430407</v>
+      </c>
+      <c r="C263" s="3">
+        <v>-4598.149359514281</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2">
+        <v>44515.0</v>
+      </c>
+      <c r="B264" s="3">
+        <v>-4475.261162538729</v>
+      </c>
+      <c r="C264" s="3">
+        <v>6311.863982885893</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2">
+        <v>44545.0</v>
+      </c>
+      <c r="B265" s="3">
+        <v>4563.862406425664</v>
+      </c>
+      <c r="C265" s="3">
+        <v>21578.83675440616</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2">
+        <v>44576.0</v>
+      </c>
+      <c r="B266" s="3">
+        <v>17620.774153507144</v>
+      </c>
+      <c r="C266" s="3">
+        <v>-7191.993543557981</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2">
+        <v>44607.0</v>
+      </c>
+      <c r="B267" s="3">
+        <v>11987.788613178325</v>
+      </c>
+      <c r="C267" s="3">
+        <v>-5560.889392690256</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2">
+        <v>44635.0</v>
+      </c>
+      <c r="B268" s="3">
+        <v>-34169.103156819816</v>
+      </c>
+      <c r="C268" s="3">
+        <v>-21310.252230418428</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2">
+        <v>44666.0</v>
+      </c>
+      <c r="B269" s="3">
+        <v>-21011.213563418347</v>
+      </c>
+      <c r="C269" s="3">
+        <v>-19789.312522609474</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2">
+        <v>44696.0</v>
+      </c>
+      <c r="B270" s="3">
+        <v>-8340.34732953768</v>
+      </c>
+      <c r="C270" s="3">
+        <v>-982.3377989096044</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2">
+        <v>44727.0</v>
+      </c>
+      <c r="B271" s="3">
+        <v>-9275.10862241598</v>
+      </c>
+      <c r="C271" s="3">
+        <v>-14364.13219810172</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2">
+        <v>44757.0</v>
+      </c>
+      <c r="B272" s="3">
+        <v>13614.43518340515</v>
+      </c>
+      <c r="C272" s="3">
+        <v>-1118.047727486546</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2">
+        <v>44788.0</v>
+      </c>
+      <c r="B273" s="3">
+        <v>-5847.845223420164</v>
+      </c>
+      <c r="C273" s="3">
+        <v>10709.094720231978</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2">
+        <v>44819.0</v>
+      </c>
+      <c r="B274" s="3">
+        <v>-3928.218624258101</v>
+      </c>
+      <c r="C274" s="3">
+        <v>-10053.177809617777</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2">
+        <v>44849.0</v>
+      </c>
+      <c r="B275" s="3">
+        <v>-44616.90669141475</v>
+      </c>
+      <c r="C275" s="3">
+        <v>-3410.649772084147</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2">
+        <v>44880.0</v>
+      </c>
+      <c r="B276" s="3">
+        <v>18491.9350075778</v>
+      </c>
+      <c r="C276" s="3">
+        <v>28436.395860006352</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2">
+        <v>44910.0</v>
+      </c>
+      <c r="B277" s="3">
+        <v>9875.272726668092</v>
+      </c>
+      <c r="C277" s="3">
+        <v>3892.3547181690456</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2">
+        <v>44941.0</v>
+      </c>
+      <c r="B278" s="3">
+        <v>-3703.3075445726095</v>
+      </c>
+      <c r="C278" s="3">
+        <v>30809.289402768925</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2">
+        <v>44972.0</v>
+      </c>
+      <c r="B279" s="3">
+        <v>-23994.891062873263</v>
+      </c>
+      <c r="C279" s="3">
+        <v>1133.3351578198972</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2">
+        <v>45000.0</v>
+      </c>
+      <c r="B280" s="3">
+        <v>-16275.850759640809</v>
+      </c>
+      <c r="C280" s="3">
+        <v>4833.286477676005</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2">
+        <v>45031.0</v>
+      </c>
+      <c r="B281" s="3">
+        <v>-18334.445204457592</v>
+      </c>
+      <c r="C281" s="3">
+        <v>-142.15359698281125</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2">
+        <v>45061.0</v>
+      </c>
+      <c r="B282" s="3">
+        <v>1108.0655433807513</v>
+      </c>
+      <c r="C282" s="3">
+        <v>12398.054936429802</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2">
+        <v>45092.0</v>
+      </c>
+      <c r="B283" s="3">
+        <v>33888.55974818528</v>
+      </c>
+      <c r="C283" s="3">
+        <v>7406.628259935363</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2">
+        <v>45122.0</v>
+      </c>
+      <c r="B284" s="3">
+        <v>-4686.188398529762</v>
+      </c>
+      <c r="C284" s="3">
+        <v>8430.132612628831</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2">
+        <v>45153.0</v>
+      </c>
+      <c r="B285" s="3">
+        <v>-15435.48910175464</v>
+      </c>
+      <c r="C285" s="3">
+        <v>-19820.76020823099</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45184.0</v>
+      </c>
+      <c r="B286" s="3">
+        <v>-3262.725938554243</v>
+      </c>
+      <c r="C286" s="3">
+        <v>-15883.29238863966</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45214.0</v>
+      </c>
+      <c r="B287" s="3">
+        <v>1750.7243638268728</v>
+      </c>
+      <c r="C287" s="3">
+        <v>-19653.687947293318</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45245.0</v>
+      </c>
+      <c r="B288" s="3">
+        <v>39025.85772243709</v>
+      </c>
+      <c r="C288" s="3">
+        <v>13519.999467663196</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45275.0</v>
+      </c>
+      <c r="B289" s="3">
+        <v>24219.94672697692</v>
+      </c>
+      <c r="C289" s="3">
+        <v>12807.65096196364</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45306.0</v>
+      </c>
+      <c r="B290" s="3">
+        <v>22581.157831300286</v>
+      </c>
+      <c r="C290" s="3">
+        <v>-2697.761191499281</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45337.0</v>
+      </c>
+      <c r="B291" s="3">
+        <v>12618.33632793527</v>
+      </c>
+      <c r="C291" s="3">
+        <v>20688.321700051714</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45366.0</v>
+      </c>
+      <c r="B292" s="3">
+        <v>2426.1391619985648</v>
+      </c>
+      <c r="C292" s="3">
+        <v>7800.976231138128</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45397.0</v>
+      </c>
+      <c r="B293" s="3">
+        <v>5148.016631387442</v>
+      </c>
+      <c r="C293" s="3">
+        <v>-2973.7019000645096</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45427.0</v>
+      </c>
+      <c r="B294" s="3">
+        <v>29708.899678979677</v>
+      </c>
+      <c r="C294" s="3">
+        <v>-2218.8261622178807</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45458.0</v>
+      </c>
+      <c r="B295" s="3">
+        <v>6872.778437559996</v>
+      </c>
+      <c r="C295" s="3">
+        <v>1151.54172812339</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45488.0</v>
+      </c>
+      <c r="B296" s="3">
+        <v>5212.089577031705</v>
+      </c>
+      <c r="C296" s="3">
+        <v>-4410.975826654046</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45519.0</v>
+      </c>
+      <c r="B297" s="3">
+        <v>14978.890909088848</v>
+      </c>
+      <c r="C297" s="3">
+        <v>2226.0271342102083</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2">
+        <v>45550.0</v>
+      </c>
+      <c r="B298" s="3">
+        <v>-26124.11642406843</v>
+      </c>
+      <c r="C298" s="3">
+        <v>25361.902209729942</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45580.0</v>
+      </c>
+      <c r="B299" s="3">
+        <v>-21140.47141912279</v>
+      </c>
+      <c r="C299" s="3">
+        <v>-25455.373528406675</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45611.0</v>
+      </c>
+      <c r="B300" s="3">
+        <v>-45991.30986269603</v>
+      </c>
+      <c r="C300" s="3">
+        <v>-29621.642339404476</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>45641.0</v>
+      </c>
+      <c r="B301" s="3">
+        <v>-15178.846895504525</v>
+      </c>
+      <c r="C301" s="3">
+        <v>-2227.780791325313</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>45672.0</v>
+      </c>
+      <c r="B302" s="3">
+        <v>4097.98432797762</v>
+      </c>
+      <c r="C302" s="3">
+        <v>-10295.159025434281</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>45703.0</v>
+      </c>
+      <c r="B303" s="3">
+        <v>-11075.078794546385</v>
+      </c>
+      <c r="C303" s="3">
+        <v>-2983.445937221684</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>45731.0</v>
+      </c>
+      <c r="B304" s="3">
+        <v>-4845.069035338766</v>
+      </c>
+      <c r="C304" s="3">
+        <v>-25827.245782994407</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/test.xlsx
+++ b/test.xlsx
@@ -43235,10 +43235,10 @@
         <v>36540.0</v>
       </c>
       <c r="B2" s="3">
-        <v>-320.7</v>
+        <v>-0.3207</v>
       </c>
       <c r="C2" s="3">
-        <v>3277.0200000000004</v>
+        <v>3.2770200000000003</v>
       </c>
     </row>
     <row r="3">
@@ -43246,10 +43246,10 @@
         <v>36571.0</v>
       </c>
       <c r="B3" s="3">
-        <v>662.9</v>
+        <v>0.6628999999999999</v>
       </c>
       <c r="C3" s="3">
-        <v>3496.65</v>
+        <v>3.4966500000000003</v>
       </c>
     </row>
     <row r="4">
@@ -43257,10 +43257,10 @@
         <v>36600.0</v>
       </c>
       <c r="B4" s="3">
-        <v>1496.8</v>
+        <v>1.4968</v>
       </c>
       <c r="C4" s="3">
-        <v>5737.22</v>
+        <v>5.737220000000001</v>
       </c>
     </row>
     <row r="5">
@@ -43268,10 +43268,10 @@
         <v>36631.0</v>
       </c>
       <c r="B5" s="3">
-        <v>673.9</v>
+        <v>0.6738999999999999</v>
       </c>
       <c r="C5" s="3">
-        <v>16.68999999999997</v>
+        <v>0.01668999999999997</v>
       </c>
     </row>
     <row r="6">
@@ -43279,10 +43279,10 @@
         <v>36661.0</v>
       </c>
       <c r="B6" s="3">
-        <v>-1693.1</v>
+        <v>-1.6930999999999998</v>
       </c>
       <c r="C6" s="3">
-        <v>1108.5900000000001</v>
+        <v>1.1085900000000002</v>
       </c>
     </row>
     <row r="7">
@@ -43290,10 +43290,10 @@
         <v>36692.0</v>
       </c>
       <c r="B7" s="3">
-        <v>-272.1</v>
+        <v>-0.2721</v>
       </c>
       <c r="C7" s="3">
-        <v>2985.34</v>
+        <v>2.9853400000000003</v>
       </c>
     </row>
     <row r="8">
@@ -43301,10 +43301,10 @@
         <v>36722.0</v>
       </c>
       <c r="B8" s="3">
-        <v>-70.0</v>
+        <v>-0.07</v>
       </c>
       <c r="C8" s="3">
-        <v>426.8599999999999</v>
+        <v>0.4268599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -43312,10 +43312,10 @@
         <v>36753.0</v>
       </c>
       <c r="B9" s="3">
-        <v>11.4</v>
+        <v>0.0114</v>
       </c>
       <c r="C9" s="3">
-        <v>1699.44</v>
+        <v>1.69944</v>
       </c>
     </row>
     <row r="10">
@@ -43323,10 +43323,10 @@
         <v>36784.0</v>
       </c>
       <c r="B10" s="3">
-        <v>-107.5</v>
+        <v>-0.1075</v>
       </c>
       <c r="C10" s="3">
-        <v>-2236.57</v>
+        <v>-2.23657</v>
       </c>
     </row>
     <row r="11">
@@ -43334,10 +43334,10 @@
         <v>36814.0</v>
       </c>
       <c r="B11" s="3">
-        <v>145.0</v>
+        <v>0.145</v>
       </c>
       <c r="C11" s="3">
-        <v>622.1899999999998</v>
+        <v>0.6221899999999998</v>
       </c>
     </row>
     <row r="12">
@@ -43345,10 +43345,10 @@
         <v>36845.0</v>
       </c>
       <c r="B12" s="3">
-        <v>-434.8</v>
+        <v>-0.4348</v>
       </c>
       <c r="C12" s="3">
-        <v>1744.0300000000002</v>
+        <v>1.7440300000000002</v>
       </c>
     </row>
     <row r="13">
@@ -43356,10 +43356,10 @@
         <v>36875.0</v>
       </c>
       <c r="B13" s="3">
-        <v>-488.4</v>
+        <v>-0.4884</v>
       </c>
       <c r="C13" s="3">
-        <v>1186.9199999999998</v>
+        <v>1.1869199999999998</v>
       </c>
     </row>
     <row r="14">
@@ -43367,10 +43367,10 @@
         <v>36906.0</v>
       </c>
       <c r="B14" s="3">
-        <v>-7.1</v>
+        <v>-0.0070999999999999995</v>
       </c>
       <c r="C14" s="3">
-        <v>4664.97</v>
+        <v>4.66497</v>
       </c>
     </row>
     <row r="15">
@@ -43378,10 +43378,10 @@
         <v>36937.0</v>
       </c>
       <c r="B15" s="3">
-        <v>139.6</v>
+        <v>0.1396</v>
       </c>
       <c r="C15" s="3">
-        <v>782.85</v>
+        <v>0.78285</v>
       </c>
     </row>
     <row r="16">
@@ -43389,10 +43389,10 @@
         <v>36965.0</v>
       </c>
       <c r="B16" s="3">
-        <v>-853.7</v>
+        <v>-0.8537</v>
       </c>
       <c r="C16" s="3">
-        <v>630.07</v>
+        <v>0.63007</v>
       </c>
     </row>
     <row r="17">
@@ -43400,10 +43400,10 @@
         <v>36996.0</v>
       </c>
       <c r="B17" s="3">
-        <v>287.6</v>
+        <v>0.2876</v>
       </c>
       <c r="C17" s="3">
-        <v>1352.59</v>
+        <v>1.35259</v>
       </c>
     </row>
     <row r="18">
@@ -43411,10 +43411,10 @@
         <v>37026.0</v>
       </c>
       <c r="B18" s="3">
-        <v>62.1</v>
+        <v>0.0621</v>
       </c>
       <c r="C18" s="3">
-        <v>2467.2</v>
+        <v>2.4671999999999996</v>
       </c>
     </row>
     <row r="19">
@@ -43422,10 +43422,10 @@
         <v>37057.0</v>
       </c>
       <c r="B19" s="3">
-        <v>885.5</v>
+        <v>0.8855</v>
       </c>
       <c r="C19" s="3">
-        <v>1081.6099999999997</v>
+        <v>1.0816099999999997</v>
       </c>
     </row>
     <row r="20">
@@ -43433,10 +43433,10 @@
         <v>37087.0</v>
       </c>
       <c r="B20" s="3">
-        <v>311.4</v>
+        <v>0.31139999999999995</v>
       </c>
       <c r="C20" s="3">
-        <v>2470.42</v>
+        <v>2.4704200000000003</v>
       </c>
     </row>
     <row r="21">
@@ -43444,10 +43444,10 @@
         <v>37118.0</v>
       </c>
       <c r="B21" s="3">
-        <v>-131.5</v>
+        <v>-0.1315</v>
       </c>
       <c r="C21" s="3">
-        <v>428.12000000000006</v>
+        <v>0.42812000000000006</v>
       </c>
     </row>
     <row r="22">
@@ -43455,10 +43455,10 @@
         <v>37149.0</v>
       </c>
       <c r="B22" s="3">
-        <v>-1698.6</v>
+        <v>-1.6985999999999999</v>
       </c>
       <c r="C22" s="3">
-        <v>-854.8399999999999</v>
+        <v>-0.8548399999999999</v>
       </c>
     </row>
     <row r="23">
@@ -43466,10 +43466,10 @@
         <v>37179.0</v>
       </c>
       <c r="B23" s="3">
-        <v>483.3</v>
+        <v>0.4833</v>
       </c>
       <c r="C23" s="3">
-        <v>2759.6800000000003</v>
+        <v>2.7596800000000004</v>
       </c>
     </row>
     <row r="24">
@@ -43477,10 +43477,10 @@
         <v>37210.0</v>
       </c>
       <c r="B24" s="3">
-        <v>534.9</v>
+        <v>0.5348999999999999</v>
       </c>
       <c r="C24" s="3">
-        <v>3501.7000000000007</v>
+        <v>3.501700000000001</v>
       </c>
     </row>
     <row r="25">
@@ -43488,10 +43488,10 @@
         <v>37240.0</v>
       </c>
       <c r="B25" s="3">
-        <v>1948.1</v>
+        <v>1.9481</v>
       </c>
       <c r="C25" s="3">
-        <v>722.91</v>
+        <v>0.7229099999999999</v>
       </c>
     </row>
     <row r="26">
@@ -43499,10 +43499,10 @@
         <v>37271.0</v>
       </c>
       <c r="B26" s="3">
-        <v>1728.9</v>
+        <v>1.7289</v>
       </c>
       <c r="C26" s="3">
-        <v>984.53</v>
+        <v>0.98453</v>
       </c>
     </row>
     <row r="27">
@@ -43510,10 +43510,10 @@
         <v>37302.0</v>
       </c>
       <c r="B27" s="3">
-        <v>-1624.6</v>
+        <v>-1.6245999999999998</v>
       </c>
       <c r="C27" s="3">
-        <v>-543.76</v>
+        <v>-0.54376</v>
       </c>
     </row>
     <row r="28">
@@ -43521,10 +43521,10 @@
         <v>37330.0</v>
       </c>
       <c r="B28" s="3">
-        <v>-568.2</v>
+        <v>-0.5682</v>
       </c>
       <c r="C28" s="3">
-        <v>1063.3600000000004</v>
+        <v>1.0633600000000003</v>
       </c>
     </row>
     <row r="29">
@@ -43532,10 +43532,10 @@
         <v>37361.0</v>
       </c>
       <c r="B29" s="3">
-        <v>141.9</v>
+        <v>0.1419</v>
       </c>
       <c r="C29" s="3">
-        <v>-208.61</v>
+        <v>-0.20861000000000002</v>
       </c>
     </row>
     <row r="30">
@@ -43543,10 +43543,10 @@
         <v>37391.0</v>
       </c>
       <c r="B30" s="3">
-        <v>1034.9</v>
+        <v>1.0349000000000002</v>
       </c>
       <c r="C30" s="3">
-        <v>-842.68</v>
+        <v>-0.84268</v>
       </c>
     </row>
     <row r="31">
@@ -43554,10 +43554,10 @@
         <v>37422.0</v>
       </c>
       <c r="B31" s="3">
-        <v>-674.2</v>
+        <v>-0.6742</v>
       </c>
       <c r="C31" s="3">
-        <v>-862.12</v>
+        <v>-0.86212</v>
       </c>
     </row>
     <row r="32">
@@ -43565,10 +43565,10 @@
         <v>37452.0</v>
       </c>
       <c r="B32" s="3">
-        <v>688.7</v>
+        <v>0.6887000000000001</v>
       </c>
       <c r="C32" s="3">
-        <v>-679.87</v>
+        <v>-0.67987</v>
       </c>
     </row>
     <row r="33">
@@ -43576,10 +43576,10 @@
         <v>37483.0</v>
       </c>
       <c r="B33" s="3">
-        <v>-450.5</v>
+        <v>-0.4505</v>
       </c>
       <c r="C33" s="3">
-        <v>178.0999999999999</v>
+        <v>0.1780999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -43587,10 +43587,10 @@
         <v>37514.0</v>
       </c>
       <c r="B34" s="3">
-        <v>1299.8</v>
+        <v>1.2997999999999998</v>
       </c>
       <c r="C34" s="3">
-        <v>-1317.7200000000003</v>
+        <v>-1.3177200000000002</v>
       </c>
     </row>
     <row r="35">
@@ -43598,10 +43598,10 @@
         <v>37544.0</v>
       </c>
       <c r="B35" s="3">
-        <v>473.5</v>
+        <v>0.4735</v>
       </c>
       <c r="C35" s="3">
-        <v>766.47</v>
+        <v>0.76647</v>
       </c>
     </row>
     <row r="36">
@@ -43609,10 +43609,10 @@
         <v>37575.0</v>
       </c>
       <c r="B36" s="3">
-        <v>1036.6</v>
+        <v>1.0366</v>
       </c>
       <c r="C36" s="3">
-        <v>2598.3</v>
+        <v>2.5983</v>
       </c>
     </row>
     <row r="37">
@@ -43620,10 +43620,10 @@
         <v>37605.0</v>
       </c>
       <c r="B37" s="3">
-        <v>1895.9</v>
+        <v>1.8959000000000001</v>
       </c>
       <c r="C37" s="3">
-        <v>386.46000000000004</v>
+        <v>0.38646</v>
       </c>
     </row>
     <row r="38">
@@ -43631,10 +43631,10 @@
         <v>37636.0</v>
       </c>
       <c r="B38" s="3">
-        <v>783.6</v>
+        <v>0.7836000000000001</v>
       </c>
       <c r="C38" s="3">
-        <v>963.97</v>
+        <v>0.96397</v>
       </c>
     </row>
     <row r="39">
@@ -43642,10 +43642,10 @@
         <v>37667.0</v>
       </c>
       <c r="B39" s="3">
-        <v>-126.9</v>
+        <v>-0.1269</v>
       </c>
       <c r="C39" s="3">
-        <v>-951.2</v>
+        <v>-0.9512</v>
       </c>
     </row>
     <row r="40">
@@ -43653,10 +43653,10 @@
         <v>37695.0</v>
       </c>
       <c r="B40" s="3">
-        <v>297.2</v>
+        <v>0.29719999999999996</v>
       </c>
       <c r="C40" s="3">
-        <v>275.96</v>
+        <v>0.27596</v>
       </c>
     </row>
     <row r="41">
@@ -43664,10 +43664,10 @@
         <v>37726.0</v>
       </c>
       <c r="B41" s="3">
-        <v>-421.2</v>
+        <v>-0.42119999999999996</v>
       </c>
       <c r="C41" s="3">
-        <v>-97.81999999999994</v>
+        <v>-0.09781999999999993</v>
       </c>
     </row>
     <row r="42">
@@ -43675,10 +43675,10 @@
         <v>37756.0</v>
       </c>
       <c r="B42" s="3">
-        <v>462.9</v>
+        <v>0.4629</v>
       </c>
       <c r="C42" s="3">
-        <v>3163.8600000000006</v>
+        <v>3.1638600000000006</v>
       </c>
     </row>
     <row r="43">
@@ -43686,10 +43686,10 @@
         <v>37787.0</v>
       </c>
       <c r="B43" s="3">
-        <v>3054.0</v>
+        <v>3.054</v>
       </c>
       <c r="C43" s="3">
-        <v>4647.0700000000015</v>
+        <v>4.647070000000001</v>
       </c>
     </row>
     <row r="44">
@@ -43697,10 +43697,10 @@
         <v>37817.0</v>
       </c>
       <c r="B44" s="3">
-        <v>54.3</v>
+        <v>0.054299999999999994</v>
       </c>
       <c r="C44" s="3">
-        <v>5018.969999999999</v>
+        <v>5.0189699999999995</v>
       </c>
     </row>
     <row r="45">
@@ -43708,10 +43708,10 @@
         <v>37848.0</v>
       </c>
       <c r="B45" s="3">
-        <v>99.9</v>
+        <v>0.0999</v>
       </c>
       <c r="C45" s="3">
-        <v>4791.17</v>
+        <v>4.79117</v>
       </c>
     </row>
     <row r="46">
@@ -43719,10 +43719,10 @@
         <v>37879.0</v>
       </c>
       <c r="B46" s="3">
-        <v>1895.5</v>
+        <v>1.8955</v>
       </c>
       <c r="C46" s="3">
-        <v>2988.9999999999995</v>
+        <v>2.9889999999999994</v>
       </c>
     </row>
     <row r="47">
@@ -43730,10 +43730,10 @@
         <v>37909.0</v>
       </c>
       <c r="B47" s="3">
-        <v>1025.6</v>
+        <v>1.0255999999999998</v>
       </c>
       <c r="C47" s="3">
-        <v>6563.8</v>
+        <v>6.5638000000000005</v>
       </c>
     </row>
     <row r="48">
@@ -43741,10 +43741,10 @@
         <v>37940.0</v>
       </c>
       <c r="B48" s="3">
-        <v>1491.6</v>
+        <v>1.4915999999999998</v>
       </c>
       <c r="C48" s="3">
-        <v>1461.3000000000002</v>
+        <v>1.4613000000000003</v>
       </c>
     </row>
     <row r="49">
@@ -43752,10 +43752,10 @@
         <v>37970.0</v>
       </c>
       <c r="B49" s="3">
-        <v>-344.8</v>
+        <v>-0.3448</v>
       </c>
       <c r="C49" s="3">
-        <v>2177.02</v>
+        <v>2.17702</v>
       </c>
     </row>
     <row r="50">
@@ -43763,10 +43763,10 @@
         <v>38001.0</v>
       </c>
       <c r="B50" s="3">
-        <v>82.4</v>
+        <v>0.0824</v>
       </c>
       <c r="C50" s="3">
-        <v>6931.77</v>
+        <v>6.93177</v>
       </c>
     </row>
     <row r="51">
@@ -43774,10 +43774,10 @@
         <v>38032.0</v>
       </c>
       <c r="B51" s="3">
-        <v>3188.2</v>
+        <v>3.1881999999999997</v>
       </c>
       <c r="C51" s="3">
-        <v>2023.98</v>
+        <v>2.02398</v>
       </c>
     </row>
     <row r="52">
@@ -43785,10 +43785,10 @@
         <v>38061.0</v>
       </c>
       <c r="B52" s="3">
-        <v>1378.5</v>
+        <v>1.3785</v>
       </c>
       <c r="C52" s="3">
-        <v>1372.0199999999995</v>
+        <v>1.3720199999999996</v>
       </c>
     </row>
     <row r="53">
@@ -43796,10 +43796,10 @@
         <v>38092.0</v>
       </c>
       <c r="B53" s="3">
-        <v>-6.2</v>
+        <v>-0.0062</v>
       </c>
       <c r="C53" s="3">
-        <v>2926.14</v>
+        <v>2.9261399999999997</v>
       </c>
     </row>
     <row r="54">
@@ -43807,10 +43807,10 @@
         <v>38122.0</v>
       </c>
       <c r="B54" s="3">
-        <v>-140.5</v>
+        <v>-0.1405</v>
       </c>
       <c r="C54" s="3">
-        <v>-4863.459999999999</v>
+        <v>-4.863459999999999</v>
       </c>
     </row>
     <row r="55">
@@ -43818,10 +43818,10 @@
         <v>38153.0</v>
       </c>
       <c r="B55" s="3">
-        <v>733.8</v>
+        <v>0.7338</v>
       </c>
       <c r="C55" s="3">
-        <v>504.59999999999997</v>
+        <v>0.5045999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -43829,10 +43829,10 @@
         <v>38183.0</v>
       </c>
       <c r="B56" s="3">
-        <v>1115.0</v>
+        <v>1.115</v>
       </c>
       <c r="C56" s="3">
-        <v>820.8299999999999</v>
+        <v>0.82083</v>
       </c>
     </row>
     <row r="57">
@@ -43840,10 +43840,10 @@
         <v>38214.0</v>
       </c>
       <c r="B57" s="3">
-        <v>-18.3</v>
+        <v>-0.0183</v>
       </c>
       <c r="C57" s="3">
-        <v>2949.66</v>
+        <v>2.9496599999999997</v>
       </c>
     </row>
     <row r="58">
@@ -43851,10 +43851,10 @@
         <v>38245.0</v>
       </c>
       <c r="B58" s="3">
-        <v>-913.1</v>
+        <v>-0.9131</v>
       </c>
       <c r="C58" s="3">
-        <v>1952.07</v>
+        <v>1.95207</v>
       </c>
     </row>
     <row r="59">
@@ -43862,10 +43862,10 @@
         <v>38275.0</v>
       </c>
       <c r="B59" s="3">
-        <v>-212.5</v>
+        <v>-0.2125</v>
       </c>
       <c r="C59" s="3">
-        <v>-79.95999999999981</v>
+        <v>-0.07995999999999981</v>
       </c>
     </row>
     <row r="60">
@@ -43873,10 +43873,10 @@
         <v>38306.0</v>
       </c>
       <c r="B60" s="3">
-        <v>1782.5</v>
+        <v>1.7825</v>
       </c>
       <c r="C60" s="3">
-        <v>3087.74</v>
+        <v>3.0877399999999997</v>
       </c>
     </row>
     <row r="61">
@@ -43884,10 +43884,10 @@
         <v>38336.0</v>
       </c>
       <c r="B61" s="3">
-        <v>1916.2</v>
+        <v>1.9162000000000001</v>
       </c>
       <c r="C61" s="3">
-        <v>-490.21000000000015</v>
+        <v>-0.49021000000000015</v>
       </c>
     </row>
     <row r="62">
@@ -43895,10 +43895,10 @@
         <v>38367.0</v>
       </c>
       <c r="B62" s="3">
-        <v>-1286.4</v>
+        <v>-1.2864</v>
       </c>
       <c r="C62" s="3">
-        <v>2730.468</v>
+        <v>2.7304679999999997</v>
       </c>
     </row>
     <row r="63">
@@ -43906,10 +43906,10 @@
         <v>38398.0</v>
       </c>
       <c r="B63" s="3">
-        <v>2157.452362327467</v>
+        <v>2.1574523623274673</v>
       </c>
       <c r="C63" s="3">
-        <v>7593.765999999999</v>
+        <v>7.593765999999999</v>
       </c>
     </row>
     <row r="64">
@@ -43917,10 +43917,10 @@
         <v>38426.0</v>
       </c>
       <c r="B64" s="3">
-        <v>1182.567662023521</v>
+        <v>1.182567662023521</v>
       </c>
       <c r="C64" s="3">
-        <v>-2615.1620000000003</v>
+        <v>-2.615162</v>
       </c>
     </row>
     <row r="65">
@@ -43928,10 +43928,10 @@
         <v>38457.0</v>
       </c>
       <c r="B65" s="3">
-        <v>-706.4760490568116</v>
+        <v>-0.7064760490568116</v>
       </c>
       <c r="C65" s="3">
-        <v>-988.9009999999998</v>
+        <v>-0.9889009999999998</v>
       </c>
     </row>
     <row r="66">
@@ -43939,10 +43939,10 @@
         <v>38487.0</v>
       </c>
       <c r="B66" s="3">
-        <v>1576.2186571703483</v>
+        <v>1.5762186571703483</v>
       </c>
       <c r="C66" s="3">
-        <v>1938.3880000000004</v>
+        <v>1.9383880000000004</v>
       </c>
     </row>
     <row r="67">
@@ -43950,10 +43950,10 @@
         <v>38518.0</v>
       </c>
       <c r="B67" s="3">
-        <v>1390.4335202761004</v>
+        <v>1.3904335202761005</v>
       </c>
       <c r="C67" s="3">
-        <v>6746.675</v>
+        <v>6.746675</v>
       </c>
     </row>
     <row r="68">
@@ -43961,10 +43961,10 @@
         <v>38548.0</v>
       </c>
       <c r="B68" s="3">
-        <v>1644.3335790753986</v>
+        <v>1.6443335790753986</v>
       </c>
       <c r="C68" s="3">
-        <v>6955.785000000001</v>
+        <v>6.9557850000000006</v>
       </c>
     </row>
     <row r="69">
@@ -43972,10 +43972,10 @@
         <v>38579.0</v>
       </c>
       <c r="B69" s="3">
-        <v>919.8609447229967</v>
+        <v>0.9198609447229967</v>
       </c>
       <c r="C69" s="3">
-        <v>656.4390000000001</v>
+        <v>0.6564390000000001</v>
       </c>
     </row>
     <row r="70">
@@ -43983,10 +43983,10 @@
         <v>38610.0</v>
       </c>
       <c r="B70" s="3">
-        <v>-453.57121046245925</v>
+        <v>-0.45357121046245924</v>
       </c>
       <c r="C70" s="3">
-        <v>494.095</v>
+        <v>0.494095</v>
       </c>
     </row>
     <row r="71">
@@ -43994,10 +43994,10 @@
         <v>38640.0</v>
       </c>
       <c r="B71" s="3">
-        <v>-1300.796624433376</v>
+        <v>-1.3007966244333762</v>
       </c>
       <c r="C71" s="3">
-        <v>-4268.979</v>
+        <v>-4.268979</v>
       </c>
     </row>
     <row r="72">
@@ -44005,10 +44005,10 @@
         <v>38671.0</v>
       </c>
       <c r="B72" s="3">
-        <v>2342.217941413838</v>
+        <v>2.342217941413838</v>
       </c>
       <c r="C72" s="3">
-        <v>9117.478000000001</v>
+        <v>9.117478</v>
       </c>
     </row>
     <row r="73">
@@ -44016,10 +44016,10 @@
         <v>38701.0</v>
       </c>
       <c r="B73" s="3">
-        <v>650.9598315698126</v>
+        <v>0.6509598315698126</v>
       </c>
       <c r="C73" s="3">
-        <v>10913.086000000001</v>
+        <v>10.913086000000002</v>
       </c>
     </row>
     <row r="74">
@@ -44027,10 +44027,10 @@
         <v>38732.0</v>
       </c>
       <c r="B74" s="3">
-        <v>804.0515235179596</v>
+        <v>0.8040515235179596</v>
       </c>
       <c r="C74" s="3">
-        <v>5820.454</v>
+        <v>5.820454</v>
       </c>
     </row>
     <row r="75">
@@ -44038,10 +44038,10 @@
         <v>38763.0</v>
       </c>
       <c r="B75" s="3">
-        <v>2886.375407113824</v>
+        <v>2.886375407113824</v>
       </c>
       <c r="C75" s="3">
-        <v>7162.300000000001</v>
+        <v>7.162300000000001</v>
       </c>
     </row>
     <row r="76">
@@ -44049,10 +44049,10 @@
         <v>38791.0</v>
       </c>
       <c r="B76" s="3">
-        <v>1521.7748909625266</v>
+        <v>1.5217748909625266</v>
       </c>
       <c r="C76" s="3">
-        <v>2414.9259999999995</v>
+        <v>2.4149259999999995</v>
       </c>
     </row>
     <row r="77">
@@ -44060,10 +44060,10 @@
         <v>38822.0</v>
       </c>
       <c r="B77" s="3">
-        <v>2840.0357898455436</v>
+        <v>2.8400357898455435</v>
       </c>
       <c r="C77" s="3">
-        <v>7070.793</v>
+        <v>7.070793</v>
       </c>
     </row>
     <row r="78">
@@ -44071,10 +44071,10 @@
         <v>38852.0</v>
       </c>
       <c r="B78" s="3">
-        <v>1550.2111011621669</v>
+        <v>1.5502111011621669</v>
       </c>
       <c r="C78" s="3">
-        <v>-9603.501</v>
+        <v>-9.603501</v>
       </c>
     </row>
     <row r="79">
@@ -44082,10 +44082,10 @@
         <v>38883.0</v>
       </c>
       <c r="B79" s="3">
-        <v>1203.7794505996849</v>
+        <v>1.2037794505996848</v>
       </c>
       <c r="C79" s="3">
-        <v>-2896.8350000000005</v>
+        <v>-2.8968350000000003</v>
       </c>
     </row>
     <row r="80">
@@ -44093,10 +44093,10 @@
         <v>38913.0</v>
       </c>
       <c r="B80" s="3">
-        <v>2053.60612926449</v>
+        <v>2.05360612926449</v>
       </c>
       <c r="C80" s="3">
-        <v>-1325.7260000000003</v>
+        <v>-1.3257260000000004</v>
       </c>
     </row>
     <row r="81">
@@ -44104,10 +44104,10 @@
         <v>38944.0</v>
       </c>
       <c r="B81" s="3">
-        <v>2335.9350062173535</v>
+        <v>2.3359350062173534</v>
       </c>
       <c r="C81" s="3">
-        <v>1258.0839999999998</v>
+        <v>1.2580839999999998</v>
       </c>
     </row>
     <row r="82">
@@ -44115,10 +44115,10 @@
         <v>38975.0</v>
       </c>
       <c r="B82" s="3">
-        <v>2348.0124308440427</v>
+        <v>2.348012430844043</v>
       </c>
       <c r="C82" s="3">
-        <v>2319.0650000000005</v>
+        <v>2.3190650000000006</v>
       </c>
     </row>
     <row r="83">
@@ -44126,10 +44126,10 @@
         <v>39005.0</v>
       </c>
       <c r="B83" s="3">
-        <v>697.8243008180702</v>
+        <v>0.6978243008180702</v>
       </c>
       <c r="C83" s="3">
-        <v>3631.182</v>
+        <v>3.631182</v>
       </c>
     </row>
     <row r="84">
@@ -44137,10 +44137,10 @@
         <v>39036.0</v>
       </c>
       <c r="B84" s="3">
-        <v>3981.281950049079</v>
+        <v>3.981281950049079</v>
       </c>
       <c r="C84" s="3">
-        <v>3872.9379999999996</v>
+        <v>3.8729379999999995</v>
       </c>
     </row>
     <row r="85">
@@ -44148,10 +44148,10 @@
         <v>39066.0</v>
       </c>
       <c r="B85" s="3">
-        <v>1551.175599429667</v>
+        <v>1.551175599429667</v>
       </c>
       <c r="C85" s="3">
-        <v>1915.1350000000002</v>
+        <v>1.9151350000000003</v>
       </c>
     </row>
     <row r="86">
@@ -44159,10 +44159,10 @@
         <v>39097.0</v>
       </c>
       <c r="B86" s="3">
-        <v>2418.71370725787</v>
+        <v>2.41871370725787</v>
       </c>
       <c r="C86" s="3">
-        <v>1041.88</v>
+        <v>1.0418800000000001</v>
       </c>
     </row>
     <row r="87">
@@ -44170,10 +44170,10 @@
         <v>39128.0</v>
       </c>
       <c r="B87" s="3">
-        <v>4515.814031298993</v>
+        <v>4.5158140312989925</v>
       </c>
       <c r="C87" s="3">
-        <v>5003.745</v>
+        <v>5.003745</v>
       </c>
     </row>
     <row r="88">
@@ -44181,10 +44181,10 @@
         <v>39156.0</v>
       </c>
       <c r="B88" s="3">
-        <v>1861.3298445776995</v>
+        <v>1.8613298445776996</v>
       </c>
       <c r="C88" s="3">
-        <v>-5111.368000000002</v>
+        <v>-5.111368000000002</v>
       </c>
     </row>
     <row r="89">
@@ -44192,10 +44192,10 @@
         <v>39187.0</v>
       </c>
       <c r="B89" s="3">
-        <v>8997.412072778197</v>
+        <v>8.997412072778197</v>
       </c>
       <c r="C89" s="3">
-        <v>7402.415999999999</v>
+        <v>7.402416</v>
       </c>
     </row>
     <row r="90">
@@ -44203,10 +44203,10 @@
         <v>39217.0</v>
       </c>
       <c r="B90" s="3">
-        <v>11082.225364447144</v>
+        <v>11.082225364447144</v>
       </c>
       <c r="C90" s="3">
-        <v>3617.92</v>
+        <v>3.6179200000000002</v>
       </c>
     </row>
     <row r="91">
@@ -44214,10 +44214,10 @@
         <v>39248.0</v>
       </c>
       <c r="B91" s="3">
-        <v>999.534189044163</v>
+        <v>0.999534189044163</v>
       </c>
       <c r="C91" s="3">
-        <v>5219.253</v>
+        <v>5.219253</v>
       </c>
     </row>
     <row r="92">
@@ -44225,10 +44225,10 @@
         <v>39278.0</v>
       </c>
       <c r="B92" s="3">
-        <v>3925.308600642833</v>
+        <v>3.925308600642833</v>
       </c>
       <c r="C92" s="3">
-        <v>876.8059999999991</v>
+        <v>0.8768059999999991</v>
       </c>
     </row>
     <row r="93">
@@ -44236,10 +44236,10 @@
         <v>39309.0</v>
       </c>
       <c r="B93" s="3">
-        <v>4135.214314301701</v>
+        <v>4.135214314301701</v>
       </c>
       <c r="C93" s="3">
-        <v>-18226.17</v>
+        <v>-18.22617</v>
       </c>
     </row>
     <row r="94">
@@ -44247,10 +44247,10 @@
         <v>39340.0</v>
       </c>
       <c r="B94" s="3">
-        <v>7050.798524798551</v>
+        <v>7.050798524798551</v>
       </c>
       <c r="C94" s="3">
-        <v>6465.569000000001</v>
+        <v>6.465569000000001</v>
       </c>
     </row>
     <row r="95">
@@ -44258,10 +44258,10 @@
         <v>39370.0</v>
       </c>
       <c r="B95" s="3">
-        <v>9494.85565823712</v>
+        <v>9.494855658237121</v>
       </c>
       <c r="C95" s="3">
-        <v>7792.483000000003</v>
+        <v>7.7924830000000025</v>
       </c>
     </row>
     <row r="96">
@@ -44269,10 +44269,10 @@
         <v>39401.0</v>
       </c>
       <c r="B96" s="3">
-        <v>11669.452532159408</v>
+        <v>11.669452532159408</v>
       </c>
       <c r="C96" s="3">
-        <v>-15328.626</v>
+        <v>-15.328626</v>
       </c>
     </row>
     <row r="97">
@@ -44280,10 +44280,10 @@
         <v>39431.0</v>
       </c>
       <c r="B97" s="3">
-        <v>10099.965880368218</v>
+        <v>10.099965880368218</v>
       </c>
       <c r="C97" s="3">
-        <v>-1207.305</v>
+        <v>-1.207305</v>
       </c>
     </row>
     <row r="98">
@@ -44291,10 +44291,10 @@
         <v>39462.0</v>
       </c>
       <c r="B98" s="3">
-        <v>11078.047214829376</v>
+        <v>11.078047214829375</v>
       </c>
       <c r="C98" s="3">
-        <v>-15876.056999999999</v>
+        <v>-15.876057</v>
       </c>
     </row>
     <row r="99">
@@ -44302,10 +44302,10 @@
         <v>39493.0</v>
       </c>
       <c r="B99" s="3">
-        <v>7754.558216712232</v>
+        <v>7.754558216712232</v>
       </c>
       <c r="C99" s="3">
-        <v>2980.1609999999996</v>
+        <v>2.9801609999999994</v>
       </c>
     </row>
     <row r="100">
@@ -44313,10 +44313,10 @@
         <v>39522.0</v>
       </c>
       <c r="B100" s="3">
-        <v>2431.135109577603</v>
+        <v>2.4311351095776033</v>
       </c>
       <c r="C100" s="3">
-        <v>-4098.311000000001</v>
+        <v>-4.098311000000001</v>
       </c>
     </row>
     <row r="101">
@@ -44324,10 +44324,10 @@
         <v>39553.0</v>
       </c>
       <c r="B101" s="3">
-        <v>9735.743082134526</v>
+        <v>9.735743082134526</v>
       </c>
       <c r="C101" s="3">
-        <v>-768.3590000000002</v>
+        <v>-0.7683590000000001</v>
       </c>
     </row>
     <row r="102">
@@ -44335,10 +44335,10 @@
         <v>39583.0</v>
       </c>
       <c r="B102" s="3">
-        <v>3165.1820795785616</v>
+        <v>3.1651820795785617</v>
       </c>
       <c r="C102" s="3">
-        <v>354.04499999999973</v>
+        <v>0.3540449999999997</v>
       </c>
     </row>
     <row r="103">
@@ -44346,10 +44346,10 @@
         <v>39614.0</v>
       </c>
       <c r="B103" s="3">
-        <v>-1581.8976725478485</v>
+        <v>-1.5818976725478484</v>
       </c>
       <c r="C103" s="3">
-        <v>-12793.078</v>
+        <v>-12.793078</v>
       </c>
     </row>
     <row r="104">
@@ -44357,10 +44357,10 @@
         <v>39644.0</v>
       </c>
       <c r="B104" s="3">
-        <v>-3526.9578348611603</v>
+        <v>-3.5269578348611605</v>
       </c>
       <c r="C104" s="3">
-        <v>-9352.043999999998</v>
+        <v>-9.352043999999998</v>
       </c>
     </row>
     <row r="105">
@@ -44368,10 +44368,10 @@
         <v>39675.0</v>
       </c>
       <c r="B105" s="3">
-        <v>-3306.50833630932</v>
+        <v>-3.30650833630932</v>
       </c>
       <c r="C105" s="3">
-        <v>-4490.316</v>
+        <v>-4.490316</v>
       </c>
     </row>
     <row r="106">
@@ -44379,10 +44379,10 @@
         <v>39706.0</v>
       </c>
       <c r="B106" s="3">
-        <v>-7206.5113268175155</v>
+        <v>-7.206511326817515</v>
       </c>
       <c r="C106" s="3">
-        <v>-8325.412</v>
+        <v>-8.325412</v>
       </c>
     </row>
     <row r="107">
@@ -44390,10 +44390,10 @@
         <v>39736.0</v>
       </c>
       <c r="B107" s="3">
-        <v>-9518.093096069524</v>
+        <v>-9.518093096069524</v>
       </c>
       <c r="C107" s="3">
-        <v>-10574.008999999998</v>
+        <v>-10.574008999999998</v>
       </c>
     </row>
     <row r="108">
@@ -44401,10 +44401,10 @@
         <v>39767.0</v>
       </c>
       <c r="B108" s="3">
-        <v>-5817.534984238542</v>
+        <v>-5.817534984238542</v>
       </c>
       <c r="C108" s="3">
-        <v>-3670.7079999999996</v>
+        <v>-3.6707079999999994</v>
       </c>
     </row>
     <row r="109">
@@ -44412,10 +44412,10 @@
         <v>39797.0</v>
       </c>
       <c r="B109" s="3">
-        <v>-1132.488538691756</v>
+        <v>-1.132488538691756</v>
       </c>
       <c r="C109" s="3">
-        <v>1747.4389999999999</v>
+        <v>1.7474389999999997</v>
       </c>
     </row>
     <row r="110">
@@ -44423,10 +44423,10 @@
         <v>39828.0</v>
       </c>
       <c r="B110" s="3">
-        <v>3012.400304200927</v>
+        <v>3.012400304200927</v>
       </c>
       <c r="C110" s="3">
-        <v>-2579.3759999999997</v>
+        <v>-2.579376</v>
       </c>
     </row>
     <row r="111">
@@ -44434,10 +44434,10 @@
         <v>39859.0</v>
       </c>
       <c r="B111" s="3">
-        <v>-1196.613459669582</v>
+        <v>-1.1966134596695819</v>
       </c>
       <c r="C111" s="3">
-        <v>-1850.665</v>
+        <v>-1.850665</v>
       </c>
     </row>
     <row r="112">
@@ -44445,10 +44445,10 @@
         <v>39887.0</v>
       </c>
       <c r="B112" s="3">
-        <v>-4816.105177882052</v>
+        <v>-4.816105177882052</v>
       </c>
       <c r="C112" s="3">
-        <v>1997.8890000000001</v>
+        <v>1.997889</v>
       </c>
     </row>
     <row r="113">
@@ -44456,10 +44456,10 @@
         <v>39918.0</v>
       </c>
       <c r="B113" s="3">
-        <v>6883.01648576061</v>
+        <v>6.88301648576061</v>
       </c>
       <c r="C113" s="3">
-        <v>7278.976</v>
+        <v>7.278975999999999</v>
       </c>
     </row>
     <row r="114">
@@ -44467,10 +44467,10 @@
         <v>39948.0</v>
       </c>
       <c r="B114" s="3">
-        <v>2583.828078791826</v>
+        <v>2.583828078791826</v>
       </c>
       <c r="C114" s="3">
-        <v>10010.221</v>
+        <v>10.010221</v>
       </c>
     </row>
     <row r="115">
@@ -44478,10 +44478,10 @@
         <v>39979.0</v>
       </c>
       <c r="B115" s="3">
-        <v>2922.5698329681045</v>
+        <v>2.9225698329681045</v>
       </c>
       <c r="C115" s="3">
-        <v>4071.0230000000006</v>
+        <v>4.071023</v>
       </c>
     </row>
     <row r="116">
@@ -44489,10 +44489,10 @@
         <v>40009.0</v>
       </c>
       <c r="B116" s="3">
-        <v>8091.664147113116</v>
+        <v>8.091664147113116</v>
       </c>
       <c r="C116" s="3">
-        <v>9365.648</v>
+        <v>9.365647999999998</v>
       </c>
     </row>
     <row r="117">
@@ -44500,10 +44500,10 @@
         <v>40040.0</v>
       </c>
       <c r="B117" s="3">
-        <v>1434.930368844884</v>
+        <v>1.434930368844884</v>
       </c>
       <c r="C117" s="3">
-        <v>5154.268</v>
+        <v>5.154268</v>
       </c>
     </row>
     <row r="118">
@@ -44511,10 +44511,10 @@
         <v>40071.0</v>
       </c>
       <c r="B118" s="3">
-        <v>6001.936768670609</v>
+        <v>6.0019367686706095</v>
       </c>
       <c r="C118" s="3">
-        <v>14077.776000000002</v>
+        <v>14.077776000000002</v>
       </c>
     </row>
     <row r="119">
@@ -44522,10 +44522,10 @@
         <v>40101.0</v>
       </c>
       <c r="B119" s="3">
-        <v>9875.305036371003</v>
+        <v>9.875305036371003</v>
       </c>
       <c r="C119" s="3">
-        <v>2916.5919999999996</v>
+        <v>2.9165919999999996</v>
       </c>
     </row>
     <row r="120">
@@ -44533,10 +44533,10 @@
         <v>40132.0</v>
       </c>
       <c r="B120" s="3">
-        <v>1245.863061168774</v>
+        <v>1.245863061168774</v>
       </c>
       <c r="C120" s="3">
-        <v>2790.3199999999997</v>
+        <v>2.79032</v>
       </c>
     </row>
     <row r="121">
@@ -44544,10 +44544,10 @@
         <v>40162.0</v>
       </c>
       <c r="B121" s="3">
-        <v>-411.5085485763924</v>
+        <v>-0.4115085485763924</v>
       </c>
       <c r="C121" s="3">
-        <v>7337.628</v>
+        <v>7.337628</v>
       </c>
     </row>
     <row r="122">
@@ -44555,10 +44555,10 @@
         <v>40193.0</v>
       </c>
       <c r="B122" s="3">
-        <v>2227.7228653680213</v>
+        <v>2.227722865368021</v>
       </c>
       <c r="C122" s="3">
-        <v>677.0749999999997</v>
+        <v>0.6770749999999996</v>
       </c>
     </row>
     <row r="123">
@@ -44566,10 +44566,10 @@
         <v>40224.0</v>
       </c>
       <c r="B123" s="3">
-        <v>2374.6583359274696</v>
+        <v>2.3746583359274696</v>
       </c>
       <c r="C123" s="3">
-        <v>-2172.161</v>
+        <v>-2.172161</v>
       </c>
     </row>
     <row r="124">
@@ -44577,10 +44577,10 @@
         <v>40252.0</v>
       </c>
       <c r="B124" s="3">
-        <v>12273.052110923023</v>
+        <v>12.273052110923024</v>
       </c>
       <c r="C124" s="3">
-        <v>14634.064999999999</v>
+        <v>14.634064999999998</v>
       </c>
     </row>
     <row r="125">
@@ -44588,10 +44588,10 @@
         <v>40283.0</v>
       </c>
       <c r="B125" s="3">
-        <v>8565.897777891729</v>
+        <v>8.56589777789173</v>
       </c>
       <c r="C125" s="3">
-        <v>11232.58</v>
+        <v>11.23258</v>
       </c>
     </row>
     <row r="126">
@@ -44599,10 +44599,10 @@
         <v>40313.0</v>
       </c>
       <c r="B126" s="3">
-        <v>3112.0369100843222</v>
+        <v>3.1120369100843224</v>
       </c>
       <c r="C126" s="3">
-        <v>-11807.876999999997</v>
+        <v>-11.807876999999996</v>
       </c>
     </row>
     <row r="127">
@@ -44610,10 +44610,10 @@
         <v>40344.0</v>
       </c>
       <c r="B127" s="3">
-        <v>3045.5812798861034</v>
+        <v>3.0455812798861035</v>
       </c>
       <c r="C127" s="3">
-        <v>4007.29</v>
+        <v>4.00729</v>
       </c>
     </row>
     <row r="128">
@@ -44621,10 +44621,10 @@
         <v>40374.0</v>
       </c>
       <c r="B128" s="3">
-        <v>11892.833822256871</v>
+        <v>11.89283382225687</v>
       </c>
       <c r="C128" s="3">
-        <v>9247.711000000001</v>
+        <v>9.247711</v>
       </c>
     </row>
     <row r="129">
@@ -44632,10 +44632,10 @@
         <v>40405.0</v>
       </c>
       <c r="B129" s="3">
-        <v>4860.224171920538</v>
+        <v>4.860224171920538</v>
       </c>
       <c r="C129" s="3">
-        <v>2444.466999999999</v>
+        <v>2.444466999999999</v>
       </c>
     </row>
     <row r="130">
@@ -44643,10 +44643,10 @@
         <v>40436.0</v>
       </c>
       <c r="B130" s="3">
-        <v>9035.133069639312</v>
+        <v>9.035133069639313</v>
       </c>
       <c r="C130" s="3">
-        <v>15740.771999999999</v>
+        <v>15.740772</v>
       </c>
     </row>
     <row r="131">
@@ -44654,10 +44654,10 @@
         <v>40466.0</v>
       </c>
       <c r="B131" s="3">
-        <v>11348.73282632205</v>
+        <v>11.348732826322049</v>
       </c>
       <c r="C131" s="3">
-        <v>13477.211000000001</v>
+        <v>13.477211</v>
       </c>
     </row>
     <row r="132">
@@ -44665,10 +44665,10 @@
         <v>40497.0</v>
       </c>
       <c r="B132" s="3">
-        <v>741.9029627941085</v>
+        <v>0.7419029627941085</v>
       </c>
       <c r="C132" s="3">
-        <v>7214.175000000001</v>
+        <v>7.214175000000001</v>
       </c>
     </row>
     <row r="133">
@@ -44676,10 +44676,10 @@
         <v>40527.0</v>
       </c>
       <c r="B133" s="3">
-        <v>-2907.976697842359</v>
+        <v>-2.907976697842359</v>
       </c>
       <c r="C133" s="3">
-        <v>9193.032000000001</v>
+        <v>9.193032</v>
       </c>
     </row>
     <row r="134">
@@ -44687,10 +44687,10 @@
         <v>40558.0</v>
       </c>
       <c r="B134" s="3">
-        <v>10932.766537207242</v>
+        <v>10.932766537207243</v>
       </c>
       <c r="C134" s="3">
-        <v>2166.5140000000006</v>
+        <v>2.1665140000000007</v>
       </c>
     </row>
     <row r="135">
@@ -44698,10 +44698,10 @@
         <v>40589.0</v>
       </c>
       <c r="B135" s="3">
-        <v>7247.26954846745</v>
+        <v>7.247269548467449</v>
       </c>
       <c r="C135" s="3">
-        <v>-8084.721999999999</v>
+        <v>-8.084722</v>
       </c>
     </row>
     <row r="136">
@@ -44709,10 +44709,10 @@
         <v>40617.0</v>
       </c>
       <c r="B136" s="3">
-        <v>9896.955017740629</v>
+        <v>9.896955017740629</v>
       </c>
       <c r="C136" s="3">
-        <v>-195.42499999999978</v>
+        <v>-0.1954249999999998</v>
       </c>
     </row>
     <row r="137">
@@ -44720,10 +44720,10 @@
         <v>40648.0</v>
       </c>
       <c r="B137" s="3">
-        <v>18035.52511644927</v>
+        <v>18.035525116449268</v>
       </c>
       <c r="C137" s="3">
-        <v>12841.913999999999</v>
+        <v>12.841914</v>
       </c>
     </row>
     <row r="138">
@@ -44731,10 +44731,10 @@
         <v>40678.0</v>
       </c>
       <c r="B138" s="3">
-        <v>6967.037699662638</v>
+        <v>6.967037699662638</v>
       </c>
       <c r="C138" s="3">
-        <v>-3702.0540000000005</v>
+        <v>-3.7020540000000004</v>
       </c>
     </row>
     <row r="139">
@@ -44742,10 +44742,10 @@
         <v>40709.0</v>
       </c>
       <c r="B139" s="3">
-        <v>4353.579317125953</v>
+        <v>4.353579317125953</v>
       </c>
       <c r="C139" s="3">
-        <v>-263.8050000000005</v>
+        <v>-0.2638050000000005</v>
       </c>
     </row>
     <row r="140">
@@ -44753,10 +44753,10 @@
         <v>40739.0</v>
       </c>
       <c r="B140" s="3">
-        <v>13757.435319634962</v>
+        <v>13.757435319634961</v>
       </c>
       <c r="C140" s="3">
-        <v>4070.5170000000003</v>
+        <v>4.070517000000001</v>
       </c>
     </row>
     <row r="141">
@@ -44764,10 +44764,10 @@
         <v>40770.0</v>
       </c>
       <c r="B141" s="3">
-        <v>3245.4198251047487</v>
+        <v>3.2454198251047486</v>
       </c>
       <c r="C141" s="3">
-        <v>-18201.064000000002</v>
+        <v>-18.201064000000002</v>
       </c>
     </row>
     <row r="142">
@@ -44775,10 +44775,10 @@
         <v>40801.0</v>
       </c>
       <c r="B142" s="3">
-        <v>-7455.537377962199</v>
+        <v>-7.455537377962199</v>
       </c>
       <c r="C142" s="3">
-        <v>-4263.669999999999</v>
+        <v>-4.263669999999999</v>
       </c>
     </row>
     <row r="143">
@@ -44786,10 +44786,10 @@
         <v>40831.0</v>
       </c>
       <c r="B143" s="3">
-        <v>4677.693508394712</v>
+        <v>4.677693508394712</v>
       </c>
       <c r="C143" s="3">
-        <v>5116.471</v>
+        <v>5.116471</v>
       </c>
     </row>
     <row r="144">
@@ -44797,10 +44797,10 @@
         <v>40862.0</v>
       </c>
       <c r="B144" s="3">
-        <v>2124.939528862875</v>
+        <v>2.1249395288628747</v>
       </c>
       <c r="C144" s="3">
-        <v>-5292.952</v>
+        <v>-5.2929520000000005</v>
       </c>
     </row>
     <row r="145">
@@ -44808,10 +44808,10 @@
         <v>40892.0</v>
       </c>
       <c r="B145" s="3">
-        <v>1271.0277013992818</v>
+        <v>1.271027701399282</v>
       </c>
       <c r="C145" s="3">
-        <v>2832.9429999999998</v>
+        <v>2.8329429999999998</v>
       </c>
     </row>
     <row r="146">
@@ -44819,10 +44819,10 @@
         <v>40923.0</v>
       </c>
       <c r="B146" s="3">
-        <v>16368.220310683313</v>
+        <v>16.368220310683313</v>
       </c>
       <c r="C146" s="3">
-        <v>10662.002</v>
+        <v>10.662002000000001</v>
       </c>
     </row>
     <row r="147">
@@ -44830,10 +44830,10 @@
         <v>40954.0</v>
       </c>
       <c r="B147" s="3">
-        <v>12467.234868485752</v>
+        <v>12.467234868485752</v>
       </c>
       <c r="C147" s="3">
-        <v>12386.242</v>
+        <v>12.386242</v>
       </c>
     </row>
     <row r="148">
@@ -44841,10 +44841,10 @@
         <v>40983.0</v>
       </c>
       <c r="B148" s="3">
-        <v>6092.783164766388</v>
+        <v>6.092783164766388</v>
       </c>
       <c r="C148" s="3">
-        <v>6402.752000000002</v>
+        <v>6.402752000000002</v>
       </c>
     </row>
     <row r="149">
@@ -44852,10 +44852,10 @@
         <v>41014.0</v>
       </c>
       <c r="B149" s="3">
-        <v>-694.7036778623072</v>
+        <v>-0.6947036778623072</v>
       </c>
       <c r="C149" s="3">
-        <v>-893.6369999999998</v>
+        <v>-0.8936369999999998</v>
       </c>
     </row>
     <row r="150">
@@ -44863,10 +44863,10 @@
         <v>41044.0</v>
       </c>
       <c r="B150" s="3">
-        <v>3343.081279474456</v>
+        <v>3.343081279474456</v>
       </c>
       <c r="C150" s="3">
-        <v>-8568.104</v>
+        <v>-8.568104</v>
       </c>
     </row>
     <row r="151">
@@ -44874,10 +44874,10 @@
         <v>41075.0</v>
       </c>
       <c r="B151" s="3">
-        <v>3991.1198684808805</v>
+        <v>3.9911198684808804</v>
       </c>
       <c r="C151" s="3">
-        <v>-1462.9699999999998</v>
+        <v>-1.4629699999999999</v>
       </c>
     </row>
     <row r="152">
@@ -44885,10 +44885,10 @@
         <v>41105.0</v>
       </c>
       <c r="B152" s="3">
-        <v>11067.127913920602</v>
+        <v>11.067127913920602</v>
       </c>
       <c r="C152" s="3">
-        <v>1737.1629999999998</v>
+        <v>1.7371629999999998</v>
       </c>
     </row>
     <row r="153">
@@ -44896,10 +44896,10 @@
         <v>41136.0</v>
       </c>
       <c r="B153" s="3">
-        <v>-216.4945629569381</v>
+        <v>-0.21649456295693809</v>
       </c>
       <c r="C153" s="3">
-        <v>11213.647</v>
+        <v>11.213647000000002</v>
       </c>
     </row>
     <row r="154">
@@ -44907,10 +44907,10 @@
         <v>41167.0</v>
       </c>
       <c r="B154" s="3">
-        <v>12172.817599738186</v>
+        <v>12.172817599738186</v>
       </c>
       <c r="C154" s="3">
-        <v>11100.334000000003</v>
+        <v>11.100334000000002</v>
       </c>
     </row>
     <row r="155">
@@ -44918,10 +44918,10 @@
         <v>41197.0</v>
       </c>
       <c r="B155" s="3">
-        <v>6522.016275973027</v>
+        <v>6.522016275973027</v>
       </c>
       <c r="C155" s="3">
-        <v>-186.3579999999997</v>
+        <v>-0.1863579999999997</v>
       </c>
     </row>
     <row r="156">
@@ -44929,10 +44929,10 @@
         <v>41228.0</v>
       </c>
       <c r="B156" s="3">
-        <v>5180.842446358305</v>
+        <v>5.180842446358305</v>
       </c>
       <c r="C156" s="3">
-        <v>2681.6449999999995</v>
+        <v>2.6816449999999996</v>
       </c>
     </row>
     <row r="157">
@@ -44940,10 +44940,10 @@
         <v>41258.0</v>
       </c>
       <c r="B157" s="3">
-        <v>5759.811359195528</v>
+        <v>5.759811359195528</v>
       </c>
       <c r="C157" s="3">
-        <v>11503.441</v>
+        <v>11.503441</v>
       </c>
     </row>
     <row r="158">
@@ -44951,10 +44951,10 @@
         <v>41289.0</v>
       </c>
       <c r="B158" s="3">
-        <v>4932.697284342943</v>
+        <v>4.932697284342943</v>
       </c>
       <c r="C158" s="3">
-        <v>5057.517000000001</v>
+        <v>5.057517000000001</v>
       </c>
     </row>
     <row r="159">
@@ -44962,10 +44962,10 @@
         <v>41320.0</v>
       </c>
       <c r="B159" s="3">
-        <v>5047.982687252201</v>
+        <v>5.047982687252201</v>
       </c>
       <c r="C159" s="3">
-        <v>7667.654</v>
+        <v>7.667654000000001</v>
       </c>
     </row>
     <row r="160">
@@ -44973,10 +44973,10 @@
         <v>41348.0</v>
       </c>
       <c r="B160" s="3">
-        <v>8545.43178519725</v>
+        <v>8.54543178519725</v>
       </c>
       <c r="C160" s="3">
-        <v>881.9299999999994</v>
+        <v>0.8819299999999994</v>
       </c>
     </row>
     <row r="161">
@@ -44984,10 +44984,10 @@
         <v>41379.0</v>
       </c>
       <c r="B161" s="3">
-        <v>12929.387551348107</v>
+        <v>12.929387551348107</v>
       </c>
       <c r="C161" s="3">
-        <v>392.3289999999996</v>
+        <v>0.3923289999999996</v>
       </c>
     </row>
     <row r="162">
@@ -44995,10 +44995,10 @@
         <v>41409.0</v>
       </c>
       <c r="B162" s="3">
-        <v>1129.2267421781878</v>
+        <v>1.1292267421781879</v>
       </c>
       <c r="C162" s="3">
-        <v>7227.919</v>
+        <v>7.227919</v>
       </c>
     </row>
     <row r="163">
@@ -45006,10 +45006,10 @@
         <v>41440.0</v>
       </c>
       <c r="B163" s="3">
-        <v>-11170.401838736725</v>
+        <v>-11.170401838736725</v>
       </c>
       <c r="C163" s="3">
-        <v>-16175.69</v>
+        <v>-16.17569</v>
       </c>
     </row>
     <row r="164">
@@ -45017,10 +45017,10 @@
         <v>41470.0</v>
       </c>
       <c r="B164" s="3">
-        <v>-1634.2617601834959</v>
+        <v>-1.634261760183496</v>
       </c>
       <c r="C164" s="3">
-        <v>2738.3200000000006</v>
+        <v>2.7383200000000008</v>
       </c>
     </row>
     <row r="165">
@@ -45028,10 +45028,10 @@
         <v>41501.0</v>
       </c>
       <c r="B165" s="3">
-        <v>-3463.09612879588</v>
+        <v>-3.46309612879588</v>
       </c>
       <c r="C165" s="3">
-        <v>-5346.425</v>
+        <v>-5.346425</v>
       </c>
     </row>
     <row r="166">
@@ -45039,10 +45039,10 @@
         <v>41532.0</v>
       </c>
       <c r="B166" s="3">
-        <v>7523.915686891502</v>
+        <v>7.5239156868915025</v>
       </c>
       <c r="C166" s="3">
-        <v>15712.862000000001</v>
+        <v>15.712862000000001</v>
       </c>
     </row>
     <row r="167">
@@ -45050,10 +45050,10 @@
         <v>41562.0</v>
       </c>
       <c r="B167" s="3">
-        <v>5217.7143207251365</v>
+        <v>5.217714320725136</v>
       </c>
       <c r="C167" s="3">
-        <v>11139.873000000001</v>
+        <v>11.139873000000001</v>
       </c>
     </row>
     <row r="168">
@@ -45061,10 +45061,10 @@
         <v>41593.0</v>
       </c>
       <c r="B168" s="3">
-        <v>-3507.169920079325</v>
+        <v>-3.507169920079325</v>
       </c>
       <c r="C168" s="3">
-        <v>-2694.8600000000006</v>
+        <v>-2.6948600000000007</v>
       </c>
     </row>
     <row r="169">
@@ -45072,10 +45072,10 @@
         <v>41623.0</v>
       </c>
       <c r="B169" s="3">
-        <v>1761.2388852404335</v>
+        <v>1.7612388852404335</v>
       </c>
       <c r="C169" s="3">
-        <v>-58.85999999999886</v>
+        <v>-0.058859999999998865</v>
       </c>
     </row>
     <row r="170">
@@ -45083,10 +45083,10 @@
         <v>41654.0</v>
       </c>
       <c r="B170" s="3">
-        <v>2349.168627639162</v>
+        <v>2.349168627639162</v>
       </c>
       <c r="C170" s="3">
-        <v>-1292.875</v>
+        <v>-1.292875</v>
       </c>
     </row>
     <row r="171">
@@ -45094,10 +45094,10 @@
         <v>41685.0</v>
       </c>
       <c r="B171" s="3">
-        <v>1474.7411913618937</v>
+        <v>1.4747411913618937</v>
       </c>
       <c r="C171" s="3">
-        <v>-1580.2990000000004</v>
+        <v>-1.5802990000000003</v>
       </c>
     </row>
     <row r="172">
@@ -45105,10 +45105,10 @@
         <v>41713.0</v>
       </c>
       <c r="B172" s="3">
-        <v>4435.652635714773</v>
+        <v>4.435652635714773</v>
       </c>
       <c r="C172" s="3">
-        <v>6505.245</v>
+        <v>6.5052449999999995</v>
       </c>
     </row>
     <row r="173">
@@ -45116,10 +45116,10 @@
         <v>41744.0</v>
       </c>
       <c r="B173" s="3">
-        <v>2837.749990162091</v>
+        <v>2.837749990162091</v>
       </c>
       <c r="C173" s="3">
-        <v>10455.527</v>
+        <v>10.455527</v>
       </c>
     </row>
     <row r="174">
@@ -45127,10 +45127,10 @@
         <v>41774.0</v>
       </c>
       <c r="B174" s="3">
-        <v>7261.490817115043</v>
+        <v>7.2614908171150425</v>
       </c>
       <c r="C174" s="3">
-        <v>6740.763</v>
+        <v>6.740763</v>
       </c>
     </row>
     <row r="175">
@@ -45138,10 +45138,10 @@
         <v>41805.0</v>
       </c>
       <c r="B175" s="3">
-        <v>4315.618098159279</v>
+        <v>4.315618098159279</v>
       </c>
       <c r="C175" s="3">
-        <v>6134.699000000001</v>
+        <v>6.134699000000001</v>
       </c>
     </row>
     <row r="176">
@@ -45149,10 +45149,10 @@
         <v>41835.0</v>
       </c>
       <c r="B176" s="3">
-        <v>11899.767423673695</v>
+        <v>11.899767423673694</v>
       </c>
       <c r="C176" s="3">
-        <v>8487.67</v>
+        <v>8.48767</v>
       </c>
     </row>
     <row r="177">
@@ -45160,10 +45160,10 @@
         <v>41866.0</v>
       </c>
       <c r="B177" s="3">
-        <v>3955.8981639748717</v>
+        <v>3.955898163974872</v>
       </c>
       <c r="C177" s="3">
-        <v>5642.236999999999</v>
+        <v>5.642236999999999</v>
       </c>
     </row>
     <row r="178">
@@ -45171,10 +45171,10 @@
         <v>41897.0</v>
       </c>
       <c r="B178" s="3">
-        <v>330.370506238862</v>
+        <v>0.330370506238862</v>
       </c>
       <c r="C178" s="3">
-        <v>-1849.313</v>
+        <v>-1.8493130000000002</v>
       </c>
     </row>
     <row r="179">
@@ -45182,10 +45182,10 @@
         <v>41927.0</v>
       </c>
       <c r="B179" s="3">
-        <v>7091.033949318885</v>
+        <v>7.091033949318885</v>
       </c>
       <c r="C179" s="3">
-        <v>-3472.106</v>
+        <v>-3.472106</v>
       </c>
     </row>
     <row r="180">
@@ -45193,10 +45193,10 @@
         <v>41958.0</v>
       </c>
       <c r="B180" s="3">
-        <v>1101.0546884820408</v>
+        <v>1.1010546884820407</v>
       </c>
       <c r="C180" s="3">
-        <v>8749.211999999998</v>
+        <v>8.749211999999998</v>
       </c>
     </row>
     <row r="181">
@@ -45204,10 +45204,10 @@
         <v>41988.0</v>
       </c>
       <c r="B181" s="3">
-        <v>-2716.281086735746</v>
+        <v>-2.716281086735746</v>
       </c>
       <c r="C181" s="3">
-        <v>-6247.214000000001</v>
+        <v>-6.2472140000000005</v>
       </c>
     </row>
     <row r="182">
@@ -45215,10 +45215,10 @@
         <v>42019.0</v>
       </c>
       <c r="B182" s="3">
-        <v>7413.214827055814</v>
+        <v>7.413214827055814</v>
       </c>
       <c r="C182" s="3">
-        <v>6004.707167003773</v>
+        <v>6.004707167003773</v>
       </c>
     </row>
     <row r="183">
@@ -45226,10 +45226,10 @@
         <v>42050.0</v>
       </c>
       <c r="B183" s="3">
-        <v>186.6702641970295</v>
+        <v>0.1866702641970295</v>
       </c>
       <c r="C183" s="3">
-        <v>8795.372230629353</v>
+        <v>8.795372230629352</v>
       </c>
     </row>
     <row r="184">
@@ -45237,10 +45237,10 @@
         <v>42078.0</v>
       </c>
       <c r="B184" s="3">
-        <v>10423.150670925797</v>
+        <v>10.423150670925798</v>
       </c>
       <c r="C184" s="3">
-        <v>4847.474702366872</v>
+        <v>4.847474702366872</v>
       </c>
     </row>
     <row r="185">
@@ -45248,10 +45248,10 @@
         <v>42109.0</v>
       </c>
       <c r="B185" s="3">
-        <v>-4094.797951568473</v>
+        <v>-4.094797951568473</v>
       </c>
       <c r="C185" s="3">
-        <v>13002.52441711078</v>
+        <v>13.00252441711078</v>
       </c>
     </row>
     <row r="186">
@@ -45259,10 +45259,10 @@
         <v>42139.0</v>
       </c>
       <c r="B186" s="3">
-        <v>4824.363904219279</v>
+        <v>4.824363904219279</v>
       </c>
       <c r="C186" s="3">
-        <v>8330.59377040704</v>
+        <v>8.33059377040704</v>
       </c>
     </row>
     <row r="187">
@@ -45270,10 +45270,10 @@
         <v>42170.0</v>
       </c>
       <c r="B187" s="3">
-        <v>3374.2019784100494</v>
+        <v>3.374201978410049</v>
       </c>
       <c r="C187" s="3">
-        <v>-541.9887875178364</v>
+        <v>-0.5419887875178364</v>
       </c>
     </row>
     <row r="188">
@@ -45281,10 +45281,10 @@
         <v>42200.0</v>
       </c>
       <c r="B188" s="3">
-        <v>-1910.4177309696483</v>
+        <v>-1.9104177309696484</v>
       </c>
       <c r="C188" s="3">
-        <v>-11195.64792811876</v>
+        <v>-11.19564792811876</v>
       </c>
     </row>
     <row r="189">
@@ -45292,10 +45292,10 @@
         <v>42231.0</v>
       </c>
       <c r="B189" s="3">
-        <v>-12408.90360897584</v>
+        <v>-12.408903608975839</v>
       </c>
       <c r="C189" s="3">
-        <v>-9612.54982666482</v>
+        <v>-9.61254982666482</v>
       </c>
     </row>
     <row r="190">
@@ -45303,10 +45303,10 @@
         <v>42262.0</v>
       </c>
       <c r="B190" s="3">
-        <v>-5997.215013860107</v>
+        <v>-5.9972150138601075</v>
       </c>
       <c r="C190" s="3">
-        <v>-5218.249945216414</v>
+        <v>-5.218249945216414</v>
       </c>
     </row>
     <row r="191">
@@ -45314,10 +45314,10 @@
         <v>42292.0</v>
       </c>
       <c r="B191" s="3">
-        <v>-1644.8245225903463</v>
+        <v>-1.6448245225903464</v>
       </c>
       <c r="C191" s="3">
-        <v>3809.2791095504963</v>
+        <v>3.8092791095504963</v>
       </c>
     </row>
     <row r="192">
@@ -45325,10 +45325,10 @@
         <v>42323.0</v>
       </c>
       <c r="B192" s="3">
-        <v>4167.453168685539</v>
+        <v>4.1674531686855385</v>
       </c>
       <c r="C192" s="3">
-        <v>-5566.106842378131</v>
+        <v>-5.56610684237813</v>
       </c>
     </row>
     <row r="193">
@@ -45336,10 +45336,10 @@
         <v>42353.0</v>
       </c>
       <c r="B193" s="3">
-        <v>-8395.184960397466</v>
+        <v>-8.395184960397467</v>
       </c>
       <c r="C193" s="3">
-        <v>-4520.358367172345</v>
+        <v>-4.520358367172346</v>
       </c>
     </row>
     <row r="194">
@@ -45347,10 +45347,10 @@
         <v>42384.0</v>
       </c>
       <c r="B194" s="3">
-        <v>-15379.561500918899</v>
+        <v>-15.379561500918898</v>
       </c>
       <c r="C194" s="3">
-        <v>-5447.477872330131</v>
+        <v>-5.447477872330131</v>
       </c>
     </row>
     <row r="195">
@@ -45358,10 +45358,10 @@
         <v>42415.0</v>
       </c>
       <c r="B195" s="3">
-        <v>-7280.248012621035</v>
+        <v>-7.280248012621035</v>
       </c>
       <c r="C195" s="3">
-        <v>1242.5023554643117</v>
+        <v>1.2425023554643118</v>
       </c>
     </row>
     <row r="196">
@@ -45369,10 +45369,10 @@
         <v>42444.0</v>
       </c>
       <c r="B196" s="3">
-        <v>3403.0712056966486</v>
+        <v>3.403071205696649</v>
       </c>
       <c r="C196" s="3">
-        <v>17891.161516865817</v>
+        <v>17.891161516865818</v>
       </c>
     </row>
     <row r="197">
@@ -45380,10 +45380,10 @@
         <v>42475.0</v>
       </c>
       <c r="B197" s="3">
-        <v>13025.086026920875</v>
+        <v>13.025086026920874</v>
       </c>
       <c r="C197" s="3">
-        <v>3647.7585803790003</v>
+        <v>3.6477585803790005</v>
       </c>
     </row>
     <row r="198">
@@ -45391,10 +45391,10 @@
         <v>42505.0</v>
       </c>
       <c r="B198" s="3">
-        <v>8404.09548594649</v>
+        <v>8.404095485946488</v>
       </c>
       <c r="C198" s="3">
-        <v>-1327.3384587427292</v>
+        <v>-1.3273384587427293</v>
       </c>
     </row>
     <row r="199">
@@ -45402,10 +45402,10 @@
         <v>42536.0</v>
       </c>
       <c r="B199" s="3">
-        <v>7601.129021642049</v>
+        <v>7.601129021642049</v>
       </c>
       <c r="C199" s="3">
-        <v>5907.764478363731</v>
+        <v>5.90776447836373</v>
       </c>
     </row>
     <row r="200">
@@ -45413,10 +45413,10 @@
         <v>42566.0</v>
       </c>
       <c r="B200" s="3">
-        <v>5043.46352358751</v>
+        <v>5.04346352358751</v>
       </c>
       <c r="C200" s="3">
-        <v>18696.78232933719</v>
+        <v>18.696782329337193</v>
       </c>
     </row>
     <row r="201">
@@ -45424,10 +45424,10 @@
         <v>42597.0</v>
       </c>
       <c r="B201" s="3">
-        <v>10524.181287951953</v>
+        <v>10.524181287951953</v>
       </c>
       <c r="C201" s="3">
-        <v>13860.192247409484</v>
+        <v>13.860192247409485</v>
       </c>
     </row>
     <row r="202">
@@ -45435,10 +45435,10 @@
         <v>42628.0</v>
       </c>
       <c r="B202" s="3">
-        <v>3835.7848545664688</v>
+        <v>3.8357848545664686</v>
       </c>
       <c r="C202" s="3">
-        <v>6330.037623253324</v>
+        <v>6.330037623253324</v>
       </c>
     </row>
     <row r="203">
@@ -45446,10 +45446,10 @@
         <v>42658.0</v>
       </c>
       <c r="B203" s="3">
-        <v>-3177.9364591386875</v>
+        <v>-3.1779364591386874</v>
       </c>
       <c r="C203" s="3">
-        <v>93.58788235872551</v>
+        <v>0.0935878823587255</v>
       </c>
     </row>
     <row r="204">
@@ -45457,10 +45457,10 @@
         <v>42689.0</v>
       </c>
       <c r="B204" s="3">
-        <v>-4508.97133426453</v>
+        <v>-4.50897133426453</v>
       </c>
       <c r="C204" s="3">
-        <v>-7805.855310147556</v>
+        <v>-7.805855310147557</v>
       </c>
     </row>
     <row r="205">
@@ -45468,10 +45468,10 @@
         <v>42719.0</v>
       </c>
       <c r="B205" s="3">
-        <v>293.81533454177986</v>
+        <v>0.2938153345417799</v>
       </c>
       <c r="C205" s="3">
-        <v>119.6796277888308</v>
+        <v>0.1196796277888308</v>
       </c>
     </row>
     <row r="206">
@@ -45479,10 +45479,10 @@
         <v>42750.0</v>
       </c>
       <c r="B206" s="3">
-        <v>7001.299323712152</v>
+        <v>7.001299323712152</v>
       </c>
       <c r="C206" s="3">
-        <v>5117.737035594597</v>
+        <v>5.117737035594597</v>
       </c>
     </row>
     <row r="207">
@@ -45490,10 +45490,10 @@
         <v>42781.0</v>
       </c>
       <c r="B207" s="3">
-        <v>3482.599033312245</v>
+        <v>3.482599033312245</v>
       </c>
       <c r="C207" s="3">
-        <v>8470.007745815477</v>
+        <v>8.470007745815478</v>
       </c>
     </row>
     <row r="208">
@@ -45501,10 +45501,10 @@
         <v>42809.0</v>
       </c>
       <c r="B208" s="3">
-        <v>4839.500712028055</v>
+        <v>4.839500712028055</v>
       </c>
       <c r="C208" s="3">
-        <v>14670.345718589922</v>
+        <v>14.670345718589923</v>
       </c>
     </row>
     <row r="209">
@@ -45512,10 +45512,10 @@
         <v>42840.0</v>
       </c>
       <c r="B209" s="3">
-        <v>13160.745209260514</v>
+        <v>13.160745209260515</v>
       </c>
       <c r="C209" s="3">
-        <v>4898.9553520760965</v>
+        <v>4.898955352076096</v>
       </c>
     </row>
     <row r="210">
@@ -45523,10 +45523,10 @@
         <v>42870.0</v>
       </c>
       <c r="B210" s="3">
-        <v>10161.34147700595</v>
+        <v>10.16134147700595</v>
       </c>
       <c r="C210" s="3">
-        <v>9564.318915888342</v>
+        <v>9.564318915888341</v>
       </c>
     </row>
     <row r="211">
@@ -45534,10 +45534,10 @@
         <v>42901.0</v>
       </c>
       <c r="B211" s="3">
-        <v>6807.068887823242</v>
+        <v>6.807068887823243</v>
       </c>
       <c r="C211" s="3">
-        <v>5640.628232035563</v>
+        <v>5.640628232035563</v>
       </c>
     </row>
     <row r="212">
@@ -45545,10 +45545,10 @@
         <v>42931.0</v>
       </c>
       <c r="B212" s="3">
-        <v>18233.623743840886</v>
+        <v>18.233623743840887</v>
       </c>
       <c r="C212" s="3">
-        <v>4370.664739899954</v>
+        <v>4.370664739899954</v>
       </c>
     </row>
     <row r="213">
@@ -45556,10 +45556,10 @@
         <v>42962.0</v>
       </c>
       <c r="B213" s="3">
-        <v>17243.59120147605</v>
+        <v>17.24359120147605</v>
       </c>
       <c r="C213" s="3">
-        <v>202.08565969394817</v>
+        <v>0.20208565969394818</v>
       </c>
     </row>
     <row r="214">
@@ -45567,10 +45567,10 @@
         <v>42993.0</v>
       </c>
       <c r="B214" s="3">
-        <v>21477.6972277101</v>
+        <v>21.477697227710102</v>
       </c>
       <c r="C214" s="3">
-        <v>-1729.4155995939013</v>
+        <v>-1.7294155995939013</v>
       </c>
     </row>
     <row r="215">
@@ -45578,10 +45578,10 @@
         <v>43023.0</v>
       </c>
       <c r="B215" s="3">
-        <v>19305.723141940653</v>
+        <v>19.305723141940653</v>
       </c>
       <c r="C215" s="3">
-        <v>6363.363513785073</v>
+        <v>6.363363513785074</v>
       </c>
     </row>
     <row r="216">
@@ -45589,10 +45589,10 @@
         <v>43054.0</v>
       </c>
       <c r="B216" s="3">
-        <v>11854.365310571833</v>
+        <v>11.854365310571833</v>
       </c>
       <c r="C216" s="3">
-        <v>4068.9704603639425</v>
+        <v>4.068970460363943</v>
       </c>
     </row>
     <row r="217">
@@ -45600,10 +45600,10 @@
         <v>43084.0</v>
       </c>
       <c r="B217" s="3">
-        <v>6466.443868012665</v>
+        <v>6.466443868012665</v>
       </c>
       <c r="C217" s="3">
-        <v>-2515.0228741490155</v>
+        <v>-2.5150228741490155</v>
       </c>
     </row>
     <row r="218">
@@ -45611,10 +45611,10 @@
         <v>43115.0</v>
       </c>
       <c r="B218" s="3">
-        <v>31373.329217347255</v>
+        <v>31.373329217347255</v>
       </c>
       <c r="C218" s="3">
-        <v>18245.78460997431</v>
+        <v>18.24578460997431</v>
       </c>
     </row>
     <row r="219">
@@ -45622,10 +45622,10 @@
         <v>43146.0</v>
       </c>
       <c r="B219" s="3">
-        <v>4169.008319180087</v>
+        <v>4.169008319180087</v>
       </c>
       <c r="C219" s="3">
-        <v>-10272.881834186112</v>
+        <v>-10.272881834186112</v>
       </c>
     </row>
     <row r="220">
@@ -45633,10 +45633,10 @@
         <v>43174.0</v>
       </c>
       <c r="B220" s="3">
-        <v>11532.710884226857</v>
+        <v>11.532710884226857</v>
       </c>
       <c r="C220" s="3">
-        <v>2543.019824211805</v>
+        <v>2.5430198242118047</v>
       </c>
     </row>
     <row r="221">
@@ -45644,10 +45644,10 @@
         <v>43205.0</v>
       </c>
       <c r="B221" s="3">
-        <v>9911.891156287596</v>
+        <v>9.911891156287597</v>
       </c>
       <c r="C221" s="3">
-        <v>204.6778085892276</v>
+        <v>0.2046778085892276</v>
       </c>
     </row>
     <row r="222">
@@ -45655,10 +45655,10 @@
         <v>43235.0</v>
       </c>
       <c r="B222" s="3">
-        <v>12989.706013614397</v>
+        <v>12.989706013614397</v>
       </c>
       <c r="C222" s="3">
-        <v>3949.2334129600385</v>
+        <v>3.9492334129600386</v>
       </c>
     </row>
     <row r="223">
@@ -45666,10 +45666,10 @@
         <v>43266.0</v>
       </c>
       <c r="B223" s="3">
-        <v>16654.686618855663</v>
+        <v>16.654686618855663</v>
       </c>
       <c r="C223" s="3">
-        <v>-2165.902221549265</v>
+        <v>-2.165902221549265</v>
       </c>
     </row>
     <row r="224">
@@ -45677,10 +45677,10 @@
         <v>43296.0</v>
       </c>
       <c r="B224" s="3">
-        <v>16288.62745720992</v>
+        <v>16.28862745720992</v>
       </c>
       <c r="C224" s="3">
-        <v>4478.0055712677995</v>
+        <v>4.4780055712678</v>
       </c>
     </row>
     <row r="225">
@@ -45688,10 +45688,10 @@
         <v>43327.0</v>
       </c>
       <c r="B225" s="3">
-        <v>25186.277986197318</v>
+        <v>25.186277986197318</v>
       </c>
       <c r="C225" s="3">
-        <v>7271.397818787554</v>
+        <v>7.271397818787554</v>
       </c>
     </row>
     <row r="226">
@@ -45699,10 +45699,10 @@
         <v>43358.0</v>
       </c>
       <c r="B226" s="3">
-        <v>459.3583868865798</v>
+        <v>0.4593583868865798</v>
       </c>
       <c r="C226" s="3">
-        <v>4080.4482099446464</v>
+        <v>4.080448209944646</v>
       </c>
     </row>
     <row r="227">
@@ -45710,10 +45710,10 @@
         <v>43388.0</v>
       </c>
       <c r="B227" s="3">
-        <v>2159.50766137582</v>
+        <v>2.15950766137582</v>
       </c>
       <c r="C227" s="3">
-        <v>-15205.624766904086</v>
+        <v>-15.205624766904085</v>
       </c>
     </row>
     <row r="228">
@@ -45721,10 +45721,10 @@
         <v>43419.0</v>
       </c>
       <c r="B228" s="3">
-        <v>-4197.912441992333</v>
+        <v>-4.197912441992333</v>
       </c>
       <c r="C228" s="3">
-        <v>10327.374651781909</v>
+        <v>10.32737465178191</v>
       </c>
     </row>
     <row r="229">
@@ -45732,10 +45732,10 @@
         <v>43449.0</v>
       </c>
       <c r="B229" s="3">
-        <v>5671.34113346204</v>
+        <v>5.67134113346204</v>
       </c>
       <c r="C229" s="3">
-        <v>1438.555815122174</v>
+        <v>1.438555815122174</v>
       </c>
     </row>
     <row r="230">
@@ -45743,10 +45743,10 @@
         <v>43480.0</v>
       </c>
       <c r="B230" s="3">
-        <v>416.38395986939776</v>
+        <v>0.41638395986939775</v>
       </c>
       <c r="C230" s="3">
-        <v>17538.119729541995</v>
+        <v>17.538119729541997</v>
       </c>
     </row>
     <row r="231">
@@ -45754,10 +45754,10 @@
         <v>43511.0</v>
       </c>
       <c r="B231" s="3">
-        <v>12843.592251124688</v>
+        <v>12.843592251124688</v>
       </c>
       <c r="C231" s="3">
-        <v>14773.183411875521</v>
+        <v>14.773183411875522</v>
       </c>
     </row>
     <row r="232">
@@ -45765,10 +45765,10 @@
         <v>43539.0</v>
       </c>
       <c r="B232" s="3">
-        <v>9252.529138935255</v>
+        <v>9.252529138935255</v>
       </c>
       <c r="C232" s="3">
-        <v>7122.724858582483</v>
+        <v>7.122724858582483</v>
       </c>
     </row>
     <row r="233">
@@ -45776,10 +45776,10 @@
         <v>43570.0</v>
       </c>
       <c r="B233" s="3">
-        <v>6751.400776907172</v>
+        <v>6.751400776907173</v>
       </c>
       <c r="C233" s="3">
-        <v>3834.558439079061</v>
+        <v>3.834558439079061</v>
       </c>
     </row>
     <row r="234">
@@ -45787,10 +45787,10 @@
         <v>43600.0</v>
       </c>
       <c r="B234" s="3">
-        <v>12594.623847310539</v>
+        <v>12.594623847310539</v>
       </c>
       <c r="C234" s="3">
-        <v>-16543.837385086685</v>
+        <v>-16.543837385086686</v>
       </c>
     </row>
     <row r="235">
@@ -45798,10 +45798,10 @@
         <v>43631.0</v>
       </c>
       <c r="B235" s="3">
-        <v>23286.110154320286</v>
+        <v>23.286110154320287</v>
       </c>
       <c r="C235" s="3">
-        <v>7303.222546007626</v>
+        <v>7.303222546007626</v>
       </c>
     </row>
     <row r="236">
@@ -45809,10 +45809,10 @@
         <v>43661.0</v>
       </c>
       <c r="B236" s="3">
-        <v>14686.45831269175</v>
+        <v>14.68645831269175</v>
       </c>
       <c r="C236" s="3">
-        <v>1147.6530357592687</v>
+        <v>1.1476530357592687</v>
       </c>
     </row>
     <row r="237">
@@ -45820,10 +45820,10 @@
         <v>43692.0</v>
       </c>
       <c r="B237" s="3">
-        <v>2365.589044731649</v>
+        <v>2.365589044731649</v>
       </c>
       <c r="C237" s="3">
-        <v>-9152.311246296766</v>
+        <v>-9.152311246296765</v>
       </c>
     </row>
     <row r="238">
@@ -45831,10 +45831,10 @@
         <v>43723.0</v>
       </c>
       <c r="B238" s="3">
-        <v>17730.802371107748</v>
+        <v>17.730802371107746</v>
       </c>
       <c r="C238" s="3">
-        <v>10278.108710537499</v>
+        <v>10.278108710537499</v>
       </c>
     </row>
     <row r="239">
@@ -45842,10 +45842,10 @@
         <v>43753.0</v>
       </c>
       <c r="B239" s="3">
-        <v>20430.292631227738</v>
+        <v>20.430292631227736</v>
       </c>
       <c r="C239" s="3">
-        <v>10616.86449362786</v>
+        <v>10.61686449362786</v>
       </c>
     </row>
     <row r="240">
@@ -45853,10 +45853,10 @@
         <v>43784.0</v>
       </c>
       <c r="B240" s="3">
-        <v>3320.4794078431205</v>
+        <v>3.3204794078431203</v>
       </c>
       <c r="C240" s="3">
-        <v>10122.50193209138</v>
+        <v>10.12250193209138</v>
       </c>
     </row>
     <row r="241">
@@ -45864,10 +45864,10 @@
         <v>43814.0</v>
       </c>
       <c r="B241" s="3">
-        <v>-6627.050016648075</v>
+        <v>-6.6270500166480755</v>
       </c>
       <c r="C241" s="3">
-        <v>13577.427574280766</v>
+        <v>13.577427574280765</v>
       </c>
     </row>
     <row r="242">
@@ -45875,10 +45875,10 @@
         <v>43845.0</v>
       </c>
       <c r="B242" s="3">
-        <v>11422.395516329898</v>
+        <v>11.422395516329898</v>
       </c>
       <c r="C242" s="3">
-        <v>2833.550305361118</v>
+        <v>2.833550305361118</v>
       </c>
     </row>
     <row r="243">
@@ -45886,10 +45886,10 @@
         <v>43876.0</v>
       </c>
       <c r="B243" s="3">
-        <v>864.7851444059673</v>
+        <v>0.8647851444059673</v>
       </c>
       <c r="C243" s="3">
-        <v>-9938.640852546388</v>
+        <v>-9.938640852546389</v>
       </c>
     </row>
     <row r="244">
@@ -45897,10 +45897,10 @@
         <v>43905.0</v>
       </c>
       <c r="B244" s="3">
-        <v>-19139.01218334642</v>
+        <v>-19.139012183346424</v>
       </c>
       <c r="C244" s="3">
-        <v>-48448.71845281473</v>
+        <v>-48.44871845281473</v>
       </c>
     </row>
     <row r="245">
@@ -45908,10 +45908,10 @@
         <v>43936.0</v>
       </c>
       <c r="B245" s="3">
-        <v>-8142.762944457598</v>
+        <v>-8.142762944457598</v>
       </c>
       <c r="C245" s="3">
-        <v>3894.0221559177035</v>
+        <v>3.8940221559177033</v>
       </c>
     </row>
     <row r="246">
@@ -45919,10 +45919,10 @@
         <v>43966.0</v>
       </c>
       <c r="B246" s="3">
-        <v>31003.966591965112</v>
+        <v>31.003966591965114</v>
       </c>
       <c r="C246" s="3">
-        <v>-1580.4200144760264</v>
+        <v>-1.5804200144760263</v>
       </c>
     </row>
     <row r="247">
@@ -45930,10 +45930,10 @@
         <v>43997.0</v>
       </c>
       <c r="B247" s="3">
-        <v>31182.946966654363</v>
+        <v>31.182946966654363</v>
       </c>
       <c r="C247" s="3">
-        <v>13808.099858558324</v>
+        <v>13.808099858558323</v>
       </c>
     </row>
     <row r="248">
@@ -45941,10 +45941,10 @@
         <v>44027.0</v>
       </c>
       <c r="B248" s="3">
-        <v>40306.0509646253</v>
+        <v>40.3060509646253</v>
       </c>
       <c r="C248" s="3">
-        <v>1755.8220898735024</v>
+        <v>1.7558220898735024</v>
       </c>
     </row>
     <row r="249">
@@ -45952,10 +45952,10 @@
         <v>44058.0</v>
       </c>
       <c r="B249" s="3">
-        <v>20414.855092796613</v>
+        <v>20.414855092796614</v>
       </c>
       <c r="C249" s="3">
-        <v>748.3816922287849</v>
+        <v>0.7483816922287849</v>
       </c>
     </row>
     <row r="250">
@@ -45963,10 +45963,10 @@
         <v>44089.0</v>
       </c>
       <c r="B250" s="3">
-        <v>31989.33602904286</v>
+        <v>31.98933602904286</v>
       </c>
       <c r="C250" s="3">
-        <v>-10426.67008210229</v>
+        <v>-10.426670082102289</v>
       </c>
     </row>
     <row r="251">
@@ -45974,10 +45974,10 @@
         <v>44119.0</v>
       </c>
       <c r="B251" s="3">
-        <v>29219.135729650534</v>
+        <v>29.219135729650535</v>
       </c>
       <c r="C251" s="3">
-        <v>8385.551725786723</v>
+        <v>8.385551725786723</v>
       </c>
     </row>
     <row r="252">
@@ -45985,10 +45985,10 @@
         <v>44150.0</v>
       </c>
       <c r="B252" s="3">
-        <v>36103.88767832232</v>
+        <v>36.103887678322316</v>
       </c>
       <c r="C252" s="3">
-        <v>32741.6858800132</v>
+        <v>32.7416858800132</v>
       </c>
     </row>
     <row r="253">
@@ -45996,10 +45996,10 @@
         <v>44180.0</v>
       </c>
       <c r="B253" s="3">
-        <v>14471.816811585966</v>
+        <v>14.471816811585967</v>
       </c>
       <c r="C253" s="3">
-        <v>27694.538194200086</v>
+        <v>27.694538194200085</v>
       </c>
     </row>
     <row r="254">
@@ -46007,10 +46007,10 @@
         <v>44211.0</v>
       </c>
       <c r="B254" s="3">
-        <v>47305.393493962954</v>
+        <v>47.30539349396295</v>
       </c>
       <c r="C254" s="3">
-        <v>-1601.51716489157</v>
+        <v>-1.60151716489157</v>
       </c>
     </row>
     <row r="255">
@@ -46018,10 +46018,10 @@
         <v>44242.0</v>
       </c>
       <c r="B255" s="3">
-        <v>43038.04509844511</v>
+        <v>43.03804509844511</v>
       </c>
       <c r="C255" s="3">
-        <v>1849.8835366608234</v>
+        <v>1.8498835366608235</v>
       </c>
     </row>
     <row r="256">
@@ -46029,10 +46029,10 @@
         <v>44270.0</v>
       </c>
       <c r="B256" s="3">
-        <v>-5374.097844403788</v>
+        <v>-5.374097844403789</v>
       </c>
       <c r="C256" s="3">
-        <v>-4574.679671769254</v>
+        <v>-4.574679671769254</v>
       </c>
     </row>
     <row r="257">
@@ -46040,10 +46040,10 @@
         <v>44301.0</v>
       </c>
       <c r="B257" s="3">
-        <v>14031.357458388398</v>
+        <v>14.031357458388399</v>
       </c>
       <c r="C257" s="3">
-        <v>11750.515042660638</v>
+        <v>11.750515042660638</v>
       </c>
     </row>
     <row r="258">
@@ -46051,10 +46051,10 @@
         <v>44331.0</v>
       </c>
       <c r="B258" s="3">
-        <v>3536.6103235853316</v>
+        <v>3.5366103235853315</v>
       </c>
       <c r="C258" s="3">
-        <v>1287.4342224540776</v>
+        <v>1.2874342224540776</v>
       </c>
     </row>
     <row r="259">
@@ -46062,10 +46062,10 @@
         <v>44362.0</v>
       </c>
       <c r="B259" s="3">
-        <v>24824.930672505172</v>
+        <v>24.82493067250517</v>
       </c>
       <c r="C259" s="3">
-        <v>3841.259634885286</v>
+        <v>3.8412596348852857</v>
       </c>
     </row>
     <row r="260">
@@ -46073,10 +46073,10 @@
         <v>44392.0</v>
       </c>
       <c r="B260" s="3">
-        <v>15053.535596490829</v>
+        <v>15.053535596490828</v>
       </c>
       <c r="C260" s="3">
-        <v>-5672.260638012698</v>
+        <v>-5.672260638012698</v>
       </c>
     </row>
     <row r="261">
@@ -46084,10 +46084,10 @@
         <v>44423.0</v>
       </c>
       <c r="B261" s="3">
-        <v>7778.705730499219</v>
+        <v>7.778705730499219</v>
       </c>
       <c r="C261" s="3">
-        <v>5321.346774524096</v>
+        <v>5.321346774524096</v>
       </c>
     </row>
     <row r="262">
@@ -46095,10 +46095,10 @@
         <v>44454.0</v>
       </c>
       <c r="B262" s="3">
-        <v>8955.327403466446</v>
+        <v>8.955327403466447</v>
       </c>
       <c r="C262" s="3">
-        <v>5153.532785710824</v>
+        <v>5.153532785710824</v>
       </c>
     </row>
     <row r="263">
@@ -46106,10 +46106,10 @@
         <v>44484.0</v>
       </c>
       <c r="B263" s="3">
-        <v>20396.12534430407</v>
+        <v>20.39612534430407</v>
       </c>
       <c r="C263" s="3">
-        <v>-4598.149359514281</v>
+        <v>-4.598149359514281</v>
       </c>
     </row>
     <row r="264">
@@ -46117,10 +46117,10 @@
         <v>44515.0</v>
       </c>
       <c r="B264" s="3">
-        <v>-4475.261162538729</v>
+        <v>-4.475261162538729</v>
       </c>
       <c r="C264" s="3">
-        <v>6311.863982885893</v>
+        <v>6.311863982885893</v>
       </c>
     </row>
     <row r="265">
@@ -46128,10 +46128,10 @@
         <v>44545.0</v>
       </c>
       <c r="B265" s="3">
-        <v>4563.862406425664</v>
+        <v>4.563862406425664</v>
       </c>
       <c r="C265" s="3">
-        <v>21578.83675440616</v>
+        <v>21.578836754406158</v>
       </c>
     </row>
     <row r="266">
@@ -46139,10 +46139,10 @@
         <v>44576.0</v>
       </c>
       <c r="B266" s="3">
-        <v>17620.774153507144</v>
+        <v>17.620774153507142</v>
       </c>
       <c r="C266" s="3">
-        <v>-7191.993543557981</v>
+        <v>-7.191993543557981</v>
       </c>
     </row>
     <row r="267">
@@ -46150,10 +46150,10 @@
         <v>44607.0</v>
       </c>
       <c r="B267" s="3">
-        <v>11987.788613178325</v>
+        <v>11.987788613178326</v>
       </c>
       <c r="C267" s="3">
-        <v>-5560.889392690256</v>
+        <v>-5.560889392690256</v>
       </c>
     </row>
     <row r="268">
@@ -46161,10 +46161,10 @@
         <v>44635.0</v>
       </c>
       <c r="B268" s="3">
-        <v>-34169.103156819816</v>
+        <v>-34.169103156819816</v>
       </c>
       <c r="C268" s="3">
-        <v>-21310.252230418428</v>
+        <v>-21.310252230418428</v>
       </c>
     </row>
     <row r="269">
@@ -46172,10 +46172,10 @@
         <v>44666.0</v>
       </c>
       <c r="B269" s="3">
-        <v>-21011.213563418347</v>
+        <v>-21.011213563418348</v>
       </c>
       <c r="C269" s="3">
-        <v>-19789.312522609474</v>
+        <v>-19.789312522609475</v>
       </c>
     </row>
     <row r="270">
@@ -46183,10 +46183,10 @@
         <v>44696.0</v>
       </c>
       <c r="B270" s="3">
-        <v>-8340.34732953768</v>
+        <v>-8.34034732953768</v>
       </c>
       <c r="C270" s="3">
-        <v>-982.3377989096044</v>
+        <v>-0.9823377989096044</v>
       </c>
     </row>
     <row r="271">
@@ -46194,10 +46194,10 @@
         <v>44727.0</v>
       </c>
       <c r="B271" s="3">
-        <v>-9275.10862241598</v>
+        <v>-9.275108622415981</v>
       </c>
       <c r="C271" s="3">
-        <v>-14364.13219810172</v>
+        <v>-14.364132198101721</v>
       </c>
     </row>
     <row r="272">
@@ -46205,10 +46205,10 @@
         <v>44757.0</v>
       </c>
       <c r="B272" s="3">
-        <v>13614.43518340515</v>
+        <v>13.614435183405151</v>
       </c>
       <c r="C272" s="3">
-        <v>-1118.047727486546</v>
+        <v>-1.118047727486546</v>
       </c>
     </row>
     <row r="273">
@@ -46216,10 +46216,10 @@
         <v>44788.0</v>
       </c>
       <c r="B273" s="3">
-        <v>-5847.845223420164</v>
+        <v>-5.847845223420164</v>
       </c>
       <c r="C273" s="3">
-        <v>10709.094720231978</v>
+        <v>10.70909472023198</v>
       </c>
     </row>
     <row r="274">
@@ -46227,10 +46227,10 @@
         <v>44819.0</v>
       </c>
       <c r="B274" s="3">
-        <v>-3928.218624258101</v>
+        <v>-3.928218624258101</v>
       </c>
       <c r="C274" s="3">
-        <v>-10053.177809617777</v>
+        <v>-10.053177809617777</v>
       </c>
     </row>
     <row r="275">
@@ -46238,10 +46238,10 @@
         <v>44849.0</v>
       </c>
       <c r="B275" s="3">
-        <v>-44616.90669141475</v>
+        <v>-44.61690669141475</v>
       </c>
       <c r="C275" s="3">
-        <v>-3410.649772084147</v>
+        <v>-3.410649772084147</v>
       </c>
     </row>
     <row r="276">
@@ -46249,10 +46249,10 @@
         <v>44880.0</v>
       </c>
       <c r="B276" s="3">
-        <v>18491.9350075778</v>
+        <v>18.491935007577798</v>
       </c>
       <c r="C276" s="3">
-        <v>28436.395860006352</v>
+        <v>28.436395860006353</v>
       </c>
     </row>
     <row r="277">
@@ -46260,10 +46260,10 @@
         <v>44910.0</v>
       </c>
       <c r="B277" s="3">
-        <v>9875.272726668092</v>
+        <v>9.875272726668092</v>
       </c>
       <c r="C277" s="3">
-        <v>3892.3547181690456</v>
+        <v>3.8923547181690457</v>
       </c>
     </row>
     <row r="278">
@@ -46271,10 +46271,10 @@
         <v>44941.0</v>
       </c>
       <c r="B278" s="3">
-        <v>-3703.3075445726095</v>
+        <v>-3.7033075445726094</v>
       </c>
       <c r="C278" s="3">
-        <v>30809.289402768925</v>
+        <v>30.809289402768925</v>
       </c>
     </row>
     <row r="279">
@@ -46282,10 +46282,10 @@
         <v>44972.0</v>
       </c>
       <c r="B279" s="3">
-        <v>-23994.891062873263</v>
+        <v>-23.99489106287326</v>
       </c>
       <c r="C279" s="3">
-        <v>1133.3351578198972</v>
+        <v>1.1333351578198971</v>
       </c>
     </row>
     <row r="280">
@@ -46293,10 +46293,10 @@
         <v>45000.0</v>
       </c>
       <c r="B280" s="3">
-        <v>-16275.850759640809</v>
+        <v>-16.275850759640807</v>
       </c>
       <c r="C280" s="3">
-        <v>4833.286477676005</v>
+        <v>4.833286477676006</v>
       </c>
     </row>
     <row r="281">
@@ -46304,10 +46304,10 @@
         <v>45031.0</v>
       </c>
       <c r="B281" s="3">
-        <v>-18334.445204457592</v>
+        <v>-18.33444520445759</v>
       </c>
       <c r="C281" s="3">
-        <v>-142.15359698281125</v>
+        <v>-0.14215359698281124</v>
       </c>
     </row>
     <row r="282">
@@ -46315,10 +46315,10 @@
         <v>45061.0</v>
       </c>
       <c r="B282" s="3">
-        <v>1108.0655433807513</v>
+        <v>1.1080655433807514</v>
       </c>
       <c r="C282" s="3">
-        <v>12398.054936429802</v>
+        <v>12.398054936429801</v>
       </c>
     </row>
     <row r="283">
@@ -46326,10 +46326,10 @@
         <v>45092.0</v>
       </c>
       <c r="B283" s="3">
-        <v>33888.55974818528</v>
+        <v>33.88855974818528</v>
       </c>
       <c r="C283" s="3">
-        <v>7406.628259935363</v>
+        <v>7.406628259935363</v>
       </c>
     </row>
     <row r="284">
@@ -46337,10 +46337,10 @@
         <v>45122.0</v>
       </c>
       <c r="B284" s="3">
-        <v>-4686.188398529762</v>
+        <v>-4.686188398529762</v>
       </c>
       <c r="C284" s="3">
-        <v>8430.132612628831</v>
+        <v>8.430132612628832</v>
       </c>
     </row>
     <row r="285">
@@ -46348,10 +46348,10 @@
         <v>45153.0</v>
       </c>
       <c r="B285" s="3">
-        <v>-15435.48910175464</v>
+        <v>-15.435489101754639</v>
       </c>
       <c r="C285" s="3">
-        <v>-19820.76020823099</v>
+        <v>-19.82076020823099</v>
       </c>
     </row>
     <row r="286">
@@ -46359,10 +46359,10 @@
         <v>45184.0</v>
       </c>
       <c r="B286" s="3">
-        <v>-3262.725938554243</v>
+        <v>-3.262725938554243</v>
       </c>
       <c r="C286" s="3">
-        <v>-15883.29238863966</v>
+        <v>-15.88329238863966</v>
       </c>
     </row>
     <row r="287">
@@ -46370,10 +46370,10 @@
         <v>45214.0</v>
       </c>
       <c r="B287" s="3">
-        <v>1750.7243638268728</v>
+        <v>1.7507243638268728</v>
       </c>
       <c r="C287" s="3">
-        <v>-19653.687947293318</v>
+        <v>-19.653687947293317</v>
       </c>
     </row>
     <row r="288">
@@ -46381,10 +46381,10 @@
         <v>45245.0</v>
       </c>
       <c r="B288" s="3">
-        <v>39025.85772243709</v>
+        <v>39.02585772243709</v>
       </c>
       <c r="C288" s="3">
-        <v>13519.999467663196</v>
+        <v>13.519999467663196</v>
       </c>
     </row>
     <row r="289">
@@ -46392,10 +46392,10 @@
         <v>45275.0</v>
       </c>
       <c r="B289" s="3">
-        <v>24219.94672697692</v>
+        <v>24.219946726976918</v>
       </c>
       <c r="C289" s="3">
-        <v>12807.65096196364</v>
+        <v>12.80765096196364</v>
       </c>
     </row>
     <row r="290">
@@ -46403,10 +46403,10 @@
         <v>45306.0</v>
       </c>
       <c r="B290" s="3">
-        <v>22581.157831300286</v>
+        <v>22.581157831300285</v>
       </c>
       <c r="C290" s="3">
-        <v>-2697.761191499281</v>
+        <v>-2.6977611914992807</v>
       </c>
     </row>
     <row r="291">
@@ -46414,10 +46414,10 @@
         <v>45337.0</v>
       </c>
       <c r="B291" s="3">
-        <v>12618.33632793527</v>
+        <v>12.618336327935271</v>
       </c>
       <c r="C291" s="3">
-        <v>20688.321700051714</v>
+        <v>20.688321700051713</v>
       </c>
     </row>
     <row r="292">
@@ -46425,10 +46425,10 @@
         <v>45366.0</v>
       </c>
       <c r="B292" s="3">
-        <v>2426.1391619985648</v>
+        <v>2.426139161998565</v>
       </c>
       <c r="C292" s="3">
-        <v>7800.976231138128</v>
+        <v>7.8009762311381285</v>
       </c>
     </row>
     <row r="293">
@@ -46436,10 +46436,10 @@
         <v>45397.0</v>
       </c>
       <c r="B293" s="3">
-        <v>5148.016631387442</v>
+        <v>5.148016631387442</v>
       </c>
       <c r="C293" s="3">
-        <v>-2973.7019000645096</v>
+        <v>-2.9737019000645097</v>
       </c>
     </row>
     <row r="294">
@@ -46447,10 +46447,10 @@
         <v>45427.0</v>
       </c>
       <c r="B294" s="3">
-        <v>29708.899678979677</v>
+        <v>29.708899678979677</v>
       </c>
       <c r="C294" s="3">
-        <v>-2218.8261622178807</v>
+        <v>-2.218826162217881</v>
       </c>
     </row>
     <row r="295">
@@ -46458,10 +46458,10 @@
         <v>45458.0</v>
       </c>
       <c r="B295" s="3">
-        <v>6872.778437559996</v>
+        <v>6.872778437559996</v>
       </c>
       <c r="C295" s="3">
-        <v>1151.54172812339</v>
+        <v>1.15154172812339</v>
       </c>
     </row>
     <row r="296">
@@ -46469,10 +46469,10 @@
         <v>45488.0</v>
       </c>
       <c r="B296" s="3">
-        <v>5212.089577031705</v>
+        <v>5.212089577031705</v>
       </c>
       <c r="C296" s="3">
-        <v>-4410.975826654046</v>
+        <v>-4.410975826654045</v>
       </c>
     </row>
     <row r="297">
@@ -46480,10 +46480,10 @@
         <v>45519.0</v>
       </c>
       <c r="B297" s="3">
-        <v>14978.890909088848</v>
+        <v>14.978890909088848</v>
       </c>
       <c r="C297" s="3">
-        <v>2226.0271342102083</v>
+        <v>2.2260271342102085</v>
       </c>
     </row>
     <row r="298">
@@ -46491,10 +46491,10 @@
         <v>45550.0</v>
       </c>
       <c r="B298" s="3">
-        <v>-26124.11642406843</v>
+        <v>-26.12411642406843</v>
       </c>
       <c r="C298" s="3">
-        <v>25361.902209729942</v>
+        <v>25.36190220972994</v>
       </c>
     </row>
     <row r="299">
@@ -46502,10 +46502,10 @@
         <v>45580.0</v>
       </c>
       <c r="B299" s="3">
-        <v>-21140.47141912279</v>
+        <v>-21.14047141912279</v>
       </c>
       <c r="C299" s="3">
-        <v>-25455.373528406675</v>
+        <v>-25.455373528406675</v>
       </c>
     </row>
     <row r="300">
@@ -46513,10 +46513,10 @@
         <v>45611.0</v>
       </c>
       <c r="B300" s="3">
-        <v>-45991.30986269603</v>
+        <v>-45.99130986269603</v>
       </c>
       <c r="C300" s="3">
-        <v>-29621.642339404476</v>
+        <v>-29.621642339404477</v>
       </c>
     </row>
     <row r="301">
@@ -46524,10 +46524,10 @@
         <v>45641.0</v>
       </c>
       <c r="B301" s="3">
-        <v>-15178.846895504525</v>
+        <v>-15.178846895504524</v>
       </c>
       <c r="C301" s="3">
-        <v>-2227.780791325313</v>
+        <v>-2.2277807913253134</v>
       </c>
     </row>
     <row r="302">
@@ -46535,10 +46535,10 @@
         <v>45672.0</v>
       </c>
       <c r="B302" s="3">
-        <v>4097.98432797762</v>
+        <v>4.09798432797762</v>
       </c>
       <c r="C302" s="3">
-        <v>-10295.159025434281</v>
+        <v>-10.29515902543428</v>
       </c>
     </row>
     <row r="303">
@@ -46546,10 +46546,10 @@
         <v>45703.0</v>
       </c>
       <c r="B303" s="3">
-        <v>-11075.078794546385</v>
+        <v>-11.075078794546386</v>
       </c>
       <c r="C303" s="3">
-        <v>-2983.445937221684</v>
+        <v>-2.983445937221684</v>
       </c>
     </row>
     <row r="304">
@@ -46557,10 +46557,10 @@
         <v>45731.0</v>
       </c>
       <c r="B304" s="3">
-        <v>-4845.069035338766</v>
+        <v>-4.845069035338766</v>
       </c>
       <c r="C304" s="3">
-        <v>-25827.245782994407</v>
+        <v>-25.827245782994407</v>
       </c>
     </row>
   </sheetData>
